--- a/liteon/dist/20261025_光寶模型_v0.1.1.xlsx
+++ b/liteon/dist/20261025_光寶模型_v0.1.1.xlsx
@@ -6461,7 +6461,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6660,7 +6660,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6781,7 +6781,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6902,7 +6902,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7023,7 +7023,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7144,7 +7144,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7230,7 +7230,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7396,7 +7396,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7614,7 +7614,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7756,7 +7756,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7849,7 +7849,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13479,7 +13479,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13603,7 +13603,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13773,7 +13773,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/liteon/dist/20261025_光寶模型_v0.1.1.xlsx
+++ b/liteon/dist/20261025_光寶模型_v0.1.1.xlsx
@@ -5435,7 +5435,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5454,7 +5454,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/liteon/dist/20261025_光寶模型_v0.1.1.xlsx
+++ b/liteon/dist/20261025_光寶模型_v0.1.1.xlsx
@@ -5748,7 +5748,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -5767,7 +5767,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6228,7 +6228,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/chip_bridge/dist/20261023_</t>
+      <t xml:space="preserve">markets/chip_bridge/dist/20261027_</t>
     </r>
     <r>
       <rPr>
@@ -6247,7 +6247,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">_v0.2.2.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -37630,7 +37630,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>34</v>
@@ -39039,7 +39039,7 @@
         <v>53</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>34</v>
@@ -39062,7 +39062,7 @@
         <v>33</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="G64" s="8" t="s">
         <v>34</v>
@@ -39108,7 +39108,7 @@
         <v>53</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>34</v>
@@ -39177,7 +39177,7 @@
         <v>53</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>34</v>
@@ -39223,7 +39223,7 @@
         <v>33</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>18.8577332859887</v>
+        <v>18.8577332859888</v>
       </c>
       <c r="G71" s="8" t="s">
         <v>34</v>
@@ -39292,7 +39292,7 @@
         <v>33</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>21.4819395843786</v>
+        <v>21.4819395843787</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>34</v>
@@ -39776,7 +39776,7 @@
       <c r="D95" s="9"/>
       <c r="E95" s="13" t="n">
         <f aca="false">(PL!G26+nim_avg)/2</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
       <c r="F95" s="9"/>
       <c r="G95" s="9" t="s">
@@ -40569,7 +40569,7 @@
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">PL!D105</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="D7" s="22" t="n">
         <f aca="false">PL!E105</f>
@@ -40623,15 +40623,15 @@
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">d_sh26</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">d_sh27</f>
-        <v>0.554488342426934</v>
+        <v>0.554488342426935</v>
       </c>
       <c r="E9" s="17" t="n">
         <f aca="false">d_sh28</f>
-        <v>0.525304745457095</v>
+        <v>0.525304745457096</v>
       </c>
       <c r="F9" s="17" t="n">
         <f aca="false">d_sh29</f>
@@ -40650,15 +40650,15 @@
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">PL!D109+d_sh26</f>
-        <v>0.759815255723818</v>
+        <v>0.759815255723819</v>
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">PL!E109+d_sh27</f>
-        <v>0.73063165875398</v>
+        <v>0.730631658753981</v>
       </c>
       <c r="E10" s="17" t="n">
         <f aca="false">PL!F109+d_sh28</f>
-        <v>0.701448061784141</v>
+        <v>0.701448061784142</v>
       </c>
       <c r="F10" s="17" t="n">
         <f aca="false">PL!G109+d_sh29</f>
@@ -40677,19 +40677,19 @@
       </c>
       <c r="C11" s="17" t="n">
         <f aca="false">1-PL!D109-d_sh26</f>
-        <v>0.240184744276183</v>
+        <v>0.240184744276181</v>
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">1-PL!E109-d_sh27</f>
-        <v>0.269368341246021</v>
+        <v>0.269368341246019</v>
       </c>
       <c r="E11" s="17" t="n">
         <f aca="false">1-PL!F109-d_sh28</f>
-        <v>0.298551938215859</v>
+        <v>0.298551938215858</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">1-PL!G109-d_sh29</f>
-        <v>0.327735535185698</v>
+        <v>0.327735535185697</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40705,15 +40705,15 @@
       </c>
       <c r="D12" s="23" t="n">
         <f aca="false">PL!E110/fx</f>
-        <v>4.40147966813923</v>
+        <v>4.40147966813924</v>
       </c>
       <c r="E12" s="23" t="n">
         <f aca="false">PL!F110/fx</f>
-        <v>5.05864636956914</v>
+        <v>5.05864636956915</v>
       </c>
       <c r="F12" s="23" t="n">
         <f aca="false">PL!G110/fx</f>
-        <v>6.48292272443381</v>
+        <v>6.48292272443382</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40737,7 +40737,7 @@
       </c>
       <c r="F13" s="23" t="n">
         <f aca="false">PL!G111/fx</f>
-        <v>7.20324747159312</v>
+        <v>7.20324747159313</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40753,7 +40753,7 @@
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">PL!E109/d_sh27</f>
-        <v>0.317668204810377</v>
+        <v>0.317668204810376</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">PL!F109/d_sh28</f>
@@ -40776,7 +40776,7 @@
       </c>
       <c r="C15" s="21" t="n">
         <f aca="false">PL!D117</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="D15" s="21" t="n">
         <f aca="false">PL!E117</f>
@@ -40788,7 +40788,7 @@
       </c>
       <c r="F15" s="21" t="n">
         <f aca="false">PL!G117</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40896,7 +40896,7 @@
       </c>
       <c r="G5" s="22" t="n">
         <f aca="false">G76</f>
-        <v>499.371972107278</v>
+        <v>499.371972107279</v>
       </c>
       <c r="H5" s="24" t="n">
         <f aca="false">H76</f>
@@ -40904,7 +40904,7 @@
       </c>
       <c r="I5" s="24" t="n">
         <f aca="false">I76</f>
-        <v>622.637441084259</v>
+        <v>622.63744108426</v>
       </c>
       <c r="J5" s="24" t="n">
         <f aca="false">J76</f>
@@ -40924,7 +40924,7 @@
       </c>
       <c r="E6" s="17" t="n">
         <f aca="false">E77</f>
-        <v>0.519920941094846</v>
+        <v>0.519920941094847</v>
       </c>
       <c r="F6" s="17" t="n">
         <f aca="false">F77</f>
@@ -40932,7 +40932,7 @@
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">G77</f>
-        <v>0.173561471727281</v>
+        <v>0.173561471727282</v>
       </c>
       <c r="H6" s="25" t="n">
         <f aca="false">H77</f>
@@ -40940,7 +40940,7 @@
       </c>
       <c r="I6" s="25" t="n">
         <f aca="false">I77</f>
-        <v>0.0978538239090938</v>
+        <v>0.0978538239090939</v>
       </c>
       <c r="J6" s="25" t="n">
         <f aca="false">J77</f>
@@ -40972,7 +40972,7 @@
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">G73</f>
-        <v>338.976351604382</v>
+        <v>338.976351604383</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41024,7 +41024,7 @@
       </c>
       <c r="F9" s="17" t="n">
         <f aca="false">F78</f>
-        <v>0.634037183770934</v>
+        <v>0.634037183770935</v>
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">G78</f>
@@ -41108,15 +41108,15 @@
       </c>
       <c r="F12" s="22" t="n">
         <f aca="false">F91</f>
-        <v>68.5975593971515</v>
+        <v>68.5975593971516</v>
       </c>
       <c r="G12" s="22" t="n">
         <f aca="false">G91</f>
-        <v>85.2853292566093</v>
+        <v>85.2853292566094</v>
       </c>
       <c r="H12" s="24" t="n">
         <f aca="false">H91</f>
-        <v>96.8592006834234</v>
+        <v>96.8592006834236</v>
       </c>
       <c r="I12" s="24" t="n">
         <f aca="false">I91</f>
@@ -41196,15 +41196,15 @@
       </c>
       <c r="H14" s="26" t="n">
         <f aca="false">H93</f>
-        <v>42.6888406280812</v>
+        <v>42.6888406280813</v>
       </c>
       <c r="I14" s="26" t="n">
         <f aca="false">I93</f>
-        <v>46.8661069217848</v>
+        <v>46.8661069217849</v>
       </c>
       <c r="J14" s="26" t="n">
         <f aca="false">J93</f>
-        <v>49.6780733370919</v>
+        <v>49.678073337092</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41220,7 +41220,7 @@
       </c>
       <c r="E15" s="17" t="n">
         <f aca="false">E94</f>
-        <v>0.886709558651466</v>
+        <v>0.886709558651469</v>
       </c>
       <c r="F15" s="17" t="n">
         <f aca="false">F94</f>
@@ -41228,7 +41228,7 @@
       </c>
       <c r="G15" s="17" t="n">
         <f aca="false">G94</f>
-        <v>0.24327060621563</v>
+        <v>0.243270606215631</v>
       </c>
       <c r="H15" s="25" t="n">
         <f aca="false">H94</f>
@@ -41240,7 +41240,7 @@
       </c>
       <c r="J15" s="25" t="n">
         <f aca="false">J94</f>
-        <v>0.0600000000000001</v>
+        <v>0.0599999999999998</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="H18" s="24" t="n">
         <f aca="false">H114</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I18" s="24" t="n">
         <f aca="false">I114</f>
@@ -41285,7 +41285,7 @@
       </c>
       <c r="J18" s="24" t="n">
         <f aca="false">J114</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41317,7 +41317,7 @@
       </c>
       <c r="I19" s="25" t="n">
         <f aca="false">I115</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J19" s="25" t="n">
         <f aca="false">J115</f>
@@ -41397,7 +41397,7 @@
       </c>
       <c r="E22" s="17" t="n">
         <f aca="false">E116</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F22" s="17" t="n">
         <f aca="false">F116</f>
@@ -41453,7 +41453,7 @@
       </c>
       <c r="E24" s="17" t="n">
         <f aca="false">E126</f>
-        <v>0.170481498867934</v>
+        <v>0.170481498867935</v>
       </c>
       <c r="F24" s="17" t="n">
         <f aca="false">F126</f>
@@ -41481,7 +41481,7 @@
       </c>
       <c r="E25" s="22" t="n">
         <f aca="false">E129</f>
-        <v>42.5255362268619</v>
+        <v>42.525536226862</v>
       </c>
       <c r="F25" s="22" t="n">
         <f aca="false">F129</f>
@@ -41489,11 +41489,11 @@
       </c>
       <c r="G25" s="22" t="n">
         <f aca="false">G129</f>
-        <v>58.3158456922108</v>
+        <v>58.3158456922109</v>
       </c>
       <c r="H25" s="24" t="n">
         <f aca="false">H129</f>
-        <v>59.342393562984</v>
+        <v>59.3423935629841</v>
       </c>
       <c r="I25" s="24" t="n">
         <f aca="false">I129</f>
@@ -41533,7 +41533,7 @@
       </c>
       <c r="H26" s="25" t="n">
         <f aca="false">H133</f>
-        <v>0.135156429558512</v>
+        <v>0.135156429558513</v>
       </c>
       <c r="I26" s="25" t="n">
         <f aca="false">I133</f>
@@ -41541,7 +41541,7 @@
       </c>
       <c r="J26" s="25" t="n">
         <f aca="false">J133</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41565,15 +41565,15 @@
       </c>
       <c r="F27" s="18" t="n">
         <f aca="false">F131</f>
-        <v>21.0058662919979</v>
+        <v>21.005866291998</v>
       </c>
       <c r="G27" s="18" t="n">
         <f aca="false">G131</f>
-        <v>25.7015939144809</v>
+        <v>25.701593914481</v>
       </c>
       <c r="H27" s="26" t="n">
         <f aca="false">H131</f>
-        <v>26.1540252596018</v>
+        <v>26.1540252596019</v>
       </c>
       <c r="I27" s="26" t="n">
         <f aca="false">I131</f>
@@ -41597,7 +41597,7 @@
       </c>
       <c r="E28" s="17" t="n">
         <f aca="false">E132</f>
-        <v>0.71236814162659</v>
+        <v>0.712368141626592</v>
       </c>
       <c r="F28" s="17" t="n">
         <f aca="false">F132</f>
@@ -41605,7 +41605,7 @@
       </c>
       <c r="G28" s="17" t="n">
         <f aca="false">G132</f>
-        <v>0.223543630965213</v>
+        <v>0.223543630965214</v>
       </c>
       <c r="H28" s="25" t="n">
         <f aca="false">H132</f>
@@ -41613,11 +41613,11 @@
       </c>
       <c r="I28" s="25" t="n">
         <f aca="false">I132</f>
-        <v>-0.0306473990530107</v>
+        <v>-0.0306473990530106</v>
       </c>
       <c r="J28" s="25" t="n">
         <f aca="false">J132</f>
-        <v>-0.0804365597655639</v>
+        <v>-0.0804365597655637</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41658,11 +41658,11 @@
       </c>
       <c r="I31" s="24" t="n">
         <f aca="false">I152</f>
-        <v>308.766940810745</v>
+        <v>308.766940810746</v>
       </c>
       <c r="J31" s="24" t="n">
         <f aca="false">J152</f>
-        <v>314.94227962696</v>
+        <v>314.942279626961</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41678,23 +41678,23 @@
       </c>
       <c r="E32" s="17" t="n">
         <f aca="false">E153</f>
-        <v>0.336007090846017</v>
+        <v>0.336007090846018</v>
       </c>
       <c r="F32" s="17" t="n">
         <f aca="false">F153</f>
-        <v>-0.0723725600685805</v>
+        <v>-0.0723725600685808</v>
       </c>
       <c r="G32" s="17" t="n">
         <f aca="false">G153</f>
-        <v>0.0712535800979055</v>
+        <v>0.0712535800979057</v>
       </c>
       <c r="H32" s="25" t="n">
         <f aca="false">H153</f>
-        <v>0.0541690533986037</v>
+        <v>0.0541690533986038</v>
       </c>
       <c r="I32" s="25" t="n">
         <f aca="false">I153</f>
-        <v>0.0370845266993018</v>
+        <v>0.0370845266993019</v>
       </c>
       <c r="J32" s="25" t="n">
         <f aca="false">J153</f>
@@ -41782,7 +41782,7 @@
       </c>
       <c r="G35" s="17" t="n">
         <f aca="false">G154</f>
-        <v>0.432081353093371</v>
+        <v>0.432081353093372</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41866,7 +41866,7 @@
       </c>
       <c r="G38" s="22" t="n">
         <f aca="false">G167</f>
-        <v>33.6617158369194</v>
+        <v>33.6617158369195</v>
       </c>
       <c r="H38" s="24" t="n">
         <f aca="false">H167</f>
@@ -41958,7 +41958,7 @@
       </c>
       <c r="J40" s="26" t="n">
         <f aca="false">J169</f>
-        <v>9.02508729248515</v>
+        <v>9.02508729248516</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41974,7 +41974,7 @@
       </c>
       <c r="E41" s="17" t="n">
         <f aca="false">E170</f>
-        <v>0.489169980269918</v>
+        <v>0.48916998026992</v>
       </c>
       <c r="F41" s="17" t="n">
         <f aca="false">F170</f>
@@ -41982,7 +41982,7 @@
       </c>
       <c r="G41" s="17" t="n">
         <f aca="false">G170</f>
-        <v>0.083006075724875</v>
+        <v>0.0830060757248752</v>
       </c>
       <c r="H41" s="25" t="n">
         <f aca="false">H170</f>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="D63" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E63" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -42179,7 +42179,7 @@
       </c>
       <c r="D67" s="23" t="n">
         <f aca="false">D65*D66/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E67" s="23" t="n">
         <f aca="false">E65*E66/1000</f>
@@ -42334,7 +42334,7 @@
       </c>
       <c r="G73" s="22" t="n">
         <f aca="false">G72/(1-x_np)</f>
-        <v>338.976351604382</v>
+        <v>338.976351604383</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>443</v>
@@ -42398,7 +42398,7 @@
       </c>
       <c r="G76" s="22" t="n">
         <f aca="false">G73+G75</f>
-        <v>499.371972107278</v>
+        <v>499.371972107279</v>
       </c>
       <c r="H76" s="24" t="n">
         <f aca="false">G76*(1+H77)</f>
@@ -42406,7 +42406,7 @@
       </c>
       <c r="I76" s="24" t="n">
         <f aca="false">H76*(1+I77)</f>
-        <v>622.637441084259</v>
+        <v>622.63744108426</v>
       </c>
       <c r="J76" s="24" t="n">
         <f aca="false">I76*(1+J77)</f>
@@ -42429,7 +42429,7 @@
       </c>
       <c r="E77" s="17" t="n">
         <f aca="false">E76/D76-1</f>
-        <v>0.519920941094846</v>
+        <v>0.519920941094847</v>
       </c>
       <c r="F77" s="17" t="n">
         <f aca="false">F76/E76-1</f>
@@ -42437,7 +42437,7 @@
       </c>
       <c r="G77" s="17" t="n">
         <f aca="false">G76/F76-1</f>
-        <v>0.173561471727281</v>
+        <v>0.173561471727282</v>
       </c>
       <c r="H77" s="25" t="n">
         <f aca="false">$G77+(fade_gA-$G77)*1/3</f>
@@ -42445,7 +42445,7 @@
       </c>
       <c r="I77" s="25" t="n">
         <f aca="false">$G77+(fade_gA-$G77)*2/3</f>
-        <v>0.0978538239090938</v>
+        <v>0.0978538239090939</v>
       </c>
       <c r="J77" s="25" t="n">
         <f aca="false">$G77+(fade_gA-$G77)*3/3</f>
@@ -42473,7 +42473,7 @@
       </c>
       <c r="F78" s="17" t="n">
         <f aca="false">F73/F76</f>
-        <v>0.634037183770934</v>
+        <v>0.634037183770935</v>
       </c>
       <c r="G78" s="17" t="n">
         <f aca="false">G73/G76</f>
@@ -42489,7 +42489,7 @@
       </c>
       <c r="D79" s="21" t="n">
         <f aca="false">D73/fx/D65*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E79" s="21" t="n">
         <f aca="false">E73/fx/E65*1000</f>
@@ -42501,7 +42501,7 @@
       </c>
       <c r="G79" s="21" t="n">
         <f aca="false">G73/fx/G65*1000</f>
-        <v>176.143316327045</v>
+        <v>176.143316327046</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42568,11 +42568,11 @@
       </c>
       <c r="E83" s="22" t="n">
         <f aca="false">E73*E82+E75*$D$81</f>
-        <v>92.5370662725746</v>
+        <v>92.5370662725747</v>
       </c>
       <c r="F83" s="22" t="n">
         <f aca="false">F73*F82+F75*$D$81</f>
-        <v>128.752225622193</v>
+        <v>128.752225622194</v>
       </c>
       <c r="G83" s="22" t="n">
         <f aca="false">G73*G82+G75*$D$81</f>
@@ -42684,7 +42684,7 @@
       </c>
       <c r="F87" s="22" t="n">
         <f aca="false">F83-F86</f>
-        <v>86.7599465751994</v>
+        <v>86.7599465751995</v>
       </c>
       <c r="G87" s="22" t="n">
         <f aca="false">G83-G86</f>
@@ -42796,15 +42796,15 @@
       </c>
       <c r="F91" s="22" t="n">
         <f aca="false">(F87+F89)*F90</f>
-        <v>68.5975593971515</v>
+        <v>68.5975593971516</v>
       </c>
       <c r="G91" s="22" t="n">
         <f aca="false">(G87+G89)*G90</f>
-        <v>85.2853292566093</v>
+        <v>85.2853292566094</v>
       </c>
       <c r="H91" s="24" t="n">
         <f aca="false">H76*H95</f>
-        <v>96.8592006834234</v>
+        <v>96.8592006834236</v>
       </c>
       <c r="I91" s="24" t="n">
         <f aca="false">I76*I95</f>
@@ -42884,15 +42884,15 @@
       </c>
       <c r="H93" s="29" t="n">
         <f aca="false">H91/H92</f>
-        <v>42.6888406280812</v>
+        <v>42.6888406280813</v>
       </c>
       <c r="I93" s="29" t="n">
         <f aca="false">I91/I92</f>
-        <v>46.8661069217848</v>
+        <v>46.8661069217849</v>
       </c>
       <c r="J93" s="29" t="n">
         <f aca="false">J91/J92</f>
-        <v>49.6780733370919</v>
+        <v>49.678073337092</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42908,7 +42908,7 @@
       </c>
       <c r="E94" s="17" t="n">
         <f aca="false">E93/D93-1</f>
-        <v>0.886709558651466</v>
+        <v>0.886709558651469</v>
       </c>
       <c r="F94" s="17" t="n">
         <f aca="false">F93/E93-1</f>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="G94" s="17" t="n">
         <f aca="false">G93/F93-1</f>
-        <v>0.24327060621563</v>
+        <v>0.243270606215631</v>
       </c>
       <c r="H94" s="25" t="n">
         <f aca="false">H93/G93-1</f>
@@ -42928,7 +42928,7 @@
       </c>
       <c r="J94" s="25" t="n">
         <f aca="false">J93/I93-1</f>
-        <v>0.0600000000000001</v>
+        <v>0.0599999999999998</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43025,7 +43025,7 @@
       </c>
       <c r="D101" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E101" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -43121,7 +43121,7 @@
       </c>
       <c r="D105" s="23" t="n">
         <f aca="false">D103*D104/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E105" s="23" t="n">
         <f aca="false">E103*E104/1000</f>
@@ -43240,7 +43240,7 @@
       </c>
       <c r="E110" s="22" t="n">
         <f aca="false">E106*E109</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F110" s="22" t="n">
         <f aca="false">F106*F109</f>
@@ -43344,7 +43344,7 @@
       </c>
       <c r="H114" s="24" t="n">
         <f aca="false">G114*(1+H115)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I114" s="24" t="n">
         <f aca="false">H114*(1+I115)</f>
@@ -43352,7 +43352,7 @@
       </c>
       <c r="J114" s="24" t="n">
         <f aca="false">I114*(1+J115)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K114" s="8" t="s">
         <v>446</v>
@@ -43387,7 +43387,7 @@
       </c>
       <c r="I115" s="25" t="n">
         <f aca="false">$G115+(fade_gB-$G115)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J115" s="25" t="n">
         <f aca="false">$G115+(fade_gB-$G115)*3/3</f>
@@ -43411,7 +43411,7 @@
       </c>
       <c r="E116" s="17" t="n">
         <f aca="false">E111/E114</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F116" s="17" t="n">
         <f aca="false">F111/F114</f>
@@ -43431,7 +43431,7 @@
       </c>
       <c r="D117" s="21" t="n">
         <f aca="false">D111/fx/D103*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E117" s="21" t="n">
         <f aca="false">E111/fx/E103*1000</f>
@@ -43443,7 +43443,7 @@
       </c>
       <c r="G117" s="21" t="n">
         <f aca="false">G111/fx/G103*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43510,15 +43510,15 @@
       </c>
       <c r="E121" s="22" t="n">
         <f aca="false">E111*E120+E113*$D$119</f>
-        <v>85.5419243406162</v>
+        <v>85.5419243406163</v>
       </c>
       <c r="F121" s="22" t="n">
         <f aca="false">F111*F120+F113*$D$119</f>
-        <v>94.39998451373</v>
+        <v>94.3999845137301</v>
       </c>
       <c r="G121" s="22" t="n">
         <f aca="false">G111*G120+G113*$D$119</f>
-        <v>112.478765927812</v>
+        <v>112.478765927813</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43566,7 +43566,7 @@
       </c>
       <c r="E123" s="22" t="n">
         <f aca="false">D123*(1+MAX(0,phi*E115))</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F123" s="22" t="n">
         <f aca="false">E123*(1+MAX(0,phi*F115))</f>
@@ -43594,7 +43594,7 @@
       </c>
       <c r="E124" s="22" t="n">
         <f aca="false">E123+0*E114</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F124" s="22" t="n">
         <f aca="false">F123+0*F114</f>
@@ -43622,15 +43622,15 @@
       </c>
       <c r="E125" s="22" t="n">
         <f aca="false">E121-E124</f>
-        <v>52.4546529300815</v>
+        <v>52.4546529300816</v>
       </c>
       <c r="F125" s="22" t="n">
         <f aca="false">F121-F124</f>
-        <v>59.2124149633085</v>
+        <v>59.2124149633086</v>
       </c>
       <c r="G125" s="22" t="n">
         <f aca="false">G121-G124</f>
-        <v>73.2313759108037</v>
+        <v>73.2313759108038</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43650,7 +43650,7 @@
       </c>
       <c r="E126" s="17" t="n">
         <f aca="false">E125/E114</f>
-        <v>0.170481498867934</v>
+        <v>0.170481498867935</v>
       </c>
       <c r="F126" s="17" t="n">
         <f aca="false">F125/F114</f>
@@ -43734,7 +43734,7 @@
       </c>
       <c r="E129" s="22" t="n">
         <f aca="false">(E125+E127)*E128</f>
-        <v>42.5255362268619</v>
+        <v>42.525536226862</v>
       </c>
       <c r="F129" s="22" t="n">
         <f aca="false">(F125+F127)*F128</f>
@@ -43742,11 +43742,11 @@
       </c>
       <c r="G129" s="22" t="n">
         <f aca="false">(G125+G127)*G128</f>
-        <v>58.3158456922108</v>
+        <v>58.3158456922109</v>
       </c>
       <c r="H129" s="24" t="n">
         <f aca="false">H114*H133</f>
-        <v>59.342393562984</v>
+        <v>59.3423935629841</v>
       </c>
       <c r="I129" s="24" t="n">
         <f aca="false">I114*I133</f>
@@ -43818,15 +43818,15 @@
       </c>
       <c r="F131" s="23" t="n">
         <f aca="false">F129/F130</f>
-        <v>21.0058662919979</v>
+        <v>21.005866291998</v>
       </c>
       <c r="G131" s="23" t="n">
         <f aca="false">G129/G130</f>
-        <v>25.7015939144809</v>
+        <v>25.701593914481</v>
       </c>
       <c r="H131" s="29" t="n">
         <f aca="false">H129/H130</f>
-        <v>26.1540252596018</v>
+        <v>26.1540252596019</v>
       </c>
       <c r="I131" s="29" t="n">
         <f aca="false">I129/I130</f>
@@ -43850,7 +43850,7 @@
       </c>
       <c r="E132" s="17" t="n">
         <f aca="false">E131/D131-1</f>
-        <v>0.71236814162659</v>
+        <v>0.712368141626592</v>
       </c>
       <c r="F132" s="17" t="n">
         <f aca="false">F131/E131-1</f>
@@ -43858,7 +43858,7 @@
       </c>
       <c r="G132" s="17" t="n">
         <f aca="false">G131/F131-1</f>
-        <v>0.223543630965213</v>
+        <v>0.223543630965214</v>
       </c>
       <c r="H132" s="25" t="n">
         <f aca="false">H131/G131-1</f>
@@ -43866,11 +43866,11 @@
       </c>
       <c r="I132" s="25" t="n">
         <f aca="false">I131/H131-1</f>
-        <v>-0.0306473990530107</v>
+        <v>-0.0306473990530106</v>
       </c>
       <c r="J132" s="25" t="n">
         <f aca="false">J131/I131-1</f>
-        <v>-0.0804365597655639</v>
+        <v>-0.0804365597655637</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43902,7 +43902,7 @@
       </c>
       <c r="H133" s="25" t="n">
         <f aca="false">$G133+(fade_mB-$G133)*1/3</f>
-        <v>0.135156429558512</v>
+        <v>0.135156429558513</v>
       </c>
       <c r="I133" s="25" t="n">
         <f aca="false">$G133+(fade_mB-$G133)*2/3</f>
@@ -43910,7 +43910,7 @@
       </c>
       <c r="J133" s="25" t="n">
         <f aca="false">$G133+(fade_mB-$G133)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43967,7 +43967,7 @@
       </c>
       <c r="D139" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E139" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -44063,7 +44063,7 @@
       </c>
       <c r="D143" s="23" t="n">
         <f aca="false">D141*D142/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E143" s="23" t="n">
         <f aca="false">E141*E142/1000</f>
@@ -44158,7 +44158,7 @@
       </c>
       <c r="F147" s="17" t="n">
         <f aca="false">$D$145*F146</f>
-        <v>0.140914653061636</v>
+        <v>0.140914653061637</v>
       </c>
       <c r="G147" s="17" t="n">
         <f aca="false">$D$145*G146</f>
@@ -44186,7 +44186,7 @@
       </c>
       <c r="F148" s="22" t="n">
         <f aca="false">F144*F147</f>
-        <v>97.1260102957275</v>
+        <v>97.1260102957276</v>
       </c>
       <c r="G148" s="22" t="n">
         <f aca="false">G144*G147</f>
@@ -44290,11 +44290,11 @@
       </c>
       <c r="I152" s="24" t="n">
         <f aca="false">H152*(1+I153)</f>
-        <v>308.766940810745</v>
+        <v>308.766940810746</v>
       </c>
       <c r="J152" s="24" t="n">
         <f aca="false">I152*(1+J153)</f>
-        <v>314.94227962696</v>
+        <v>314.942279626961</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>446</v>
@@ -44313,23 +44313,23 @@
       </c>
       <c r="E153" s="17" t="n">
         <f aca="false">E152/D152-1</f>
-        <v>0.336007090846017</v>
+        <v>0.336007090846018</v>
       </c>
       <c r="F153" s="17" t="n">
         <f aca="false">F152/E152-1</f>
-        <v>-0.0723725600685805</v>
+        <v>-0.0723725600685808</v>
       </c>
       <c r="G153" s="17" t="n">
         <f aca="false">G152/F152-1</f>
-        <v>0.0712535800979055</v>
+        <v>0.0712535800979057</v>
       </c>
       <c r="H153" s="25" t="n">
         <f aca="false">$G153+(fade_gC-$G153)*1/3</f>
-        <v>0.0541690533986037</v>
+        <v>0.0541690533986038</v>
       </c>
       <c r="I153" s="25" t="n">
         <f aca="false">$G153+(fade_gC-$G153)*2/3</f>
-        <v>0.0370845266993018</v>
+        <v>0.0370845266993019</v>
       </c>
       <c r="J153" s="25" t="n">
         <f aca="false">$G153+(fade_gC-$G153)*3/3</f>
@@ -44361,7 +44361,7 @@
       </c>
       <c r="G154" s="17" t="n">
         <f aca="false">G149/G152</f>
-        <v>0.432081353093371</v>
+        <v>0.432081353093372</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44373,11 +44373,11 @@
       </c>
       <c r="D155" s="21" t="n">
         <f aca="false">D149/fx/D141*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E155" s="21" t="n">
         <f aca="false">E149/fx/E141*1000</f>
-        <v>99.8145459186591</v>
+        <v>99.8145459186593</v>
       </c>
       <c r="F155" s="21" t="n">
         <f aca="false">F149/fx/F141*1000</f>
@@ -44452,11 +44452,11 @@
       </c>
       <c r="E159" s="22" t="n">
         <f aca="false">E149*E158+E151*$D$157</f>
-        <v>76.301187881616</v>
+        <v>76.3011878816161</v>
       </c>
       <c r="F159" s="22" t="n">
         <f aca="false">F149*F158+F151*$D$157</f>
-        <v>68.5369584652214</v>
+        <v>68.5369584652215</v>
       </c>
       <c r="G159" s="22" t="n">
         <f aca="false">G149*G158+G151*$D$157</f>
@@ -44684,7 +44684,7 @@
       </c>
       <c r="G167" s="22" t="n">
         <f aca="false">(G163+G165)*G166</f>
-        <v>33.6617158369194</v>
+        <v>33.6617158369195</v>
       </c>
       <c r="H167" s="24" t="n">
         <f aca="false">H152*H171</f>
@@ -44776,7 +44776,7 @@
       </c>
       <c r="J169" s="29" t="n">
         <f aca="false">J167/J168</f>
-        <v>9.02508729248515</v>
+        <v>9.02508729248516</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44792,7 +44792,7 @@
       </c>
       <c r="E170" s="17" t="n">
         <f aca="false">E169/D169-1</f>
-        <v>0.489169980269918</v>
+        <v>0.48916998026992</v>
       </c>
       <c r="F170" s="17" t="n">
         <f aca="false">F169/E169-1</f>
@@ -44800,7 +44800,7 @@
       </c>
       <c r="G170" s="17" t="n">
         <f aca="false">G169/F169-1</f>
-        <v>0.083006075724875</v>
+        <v>0.0830060757248752</v>
       </c>
       <c r="H170" s="25" t="n">
         <f aca="false">H169/G169-1</f>
@@ -44950,7 +44950,7 @@
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">PL!F27</f>
-        <v>21.0058662919979</v>
+        <v>21.005866291998</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">PL!F40</f>
@@ -44967,7 +44967,7 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">PL!G27</f>
-        <v>25.7015939144809</v>
+        <v>25.701593914481</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">PL!G40</f>
@@ -44980,11 +44980,11 @@
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">PL!H14</f>
-        <v>42.6888406280812</v>
+        <v>42.6888406280813</v>
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">PL!H27</f>
-        <v>26.1540252596018</v>
+        <v>26.1540252596019</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">PL!H40</f>
@@ -44997,7 +44997,7 @@
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">PL!I14</f>
-        <v>46.8661069217848</v>
+        <v>46.8661069217849</v>
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">PL!I27</f>
@@ -45014,7 +45014,7 @@
       </c>
       <c r="B13" s="18" t="n">
         <f aca="false">PL!J14</f>
-        <v>49.6780733370919</v>
+        <v>49.678073337092</v>
       </c>
       <c r="C13" s="18" t="n">
         <f aca="false">PL!J27</f>
@@ -45022,7 +45022,7 @@
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">PL!J40</f>
-        <v>9.02508729248515</v>
+        <v>9.02508729248516</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45103,11 +45103,11 @@
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">C11*(1-$B$15)</f>
-        <v>19.5854128042811</v>
+        <v>19.5854128042812</v>
       </c>
       <c r="D19" s="18" t="n">
         <f aca="false">D11*(1-$B$15)</f>
-        <v>9.93735526250219</v>
+        <v>9.9373552625022</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45116,7 +45116,7 @@
       </c>
       <c r="B20" s="18" t="n">
         <f aca="false">B12*(1-$B$15)</f>
-        <v>35.0956321821151</v>
+        <v>35.0956321821152</v>
       </c>
       <c r="C20" s="18" t="n">
         <f aca="false">C12*(1-$B$15)</f>
@@ -45124,7 +45124,7 @@
       </c>
       <c r="D20" s="18" t="n">
         <f aca="false">D12*(1-$B$15)</f>
-        <v>8.46589290908275</v>
+        <v>8.46589290908276</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45133,7 +45133,7 @@
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">B13*(1-$B$15)</f>
-        <v>37.201370113042</v>
+        <v>37.2013701130421</v>
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">C13*(1-$B$15)</f>
@@ -45154,11 +45154,11 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(C16:C21,1/(1+tp_r)^{1;2;3;4;5;6})+C21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>246.053203604463</v>
+        <v>246.053203604464</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(D16:D21,1/(1+tp_r)^{1;2;3;4;5;6})+D21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>109.905793899935</v>
+        <v>109.905793899936</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>480</v>
@@ -45170,7 +45170,7 @@
       </c>
       <c r="B23" s="18" t="n">
         <f aca="false">B22*(1+tp_r)</f>
-        <v>530.780830267397</v>
+        <v>530.780830267398</v>
       </c>
       <c r="C23" s="18" t="n">
         <f aca="false">C22*(1+tp_r)</f>
@@ -45321,7 +45321,7 @@
       </c>
       <c r="B35" s="18" t="n">
         <f aca="false">tp_wA*(2/12*B8+10/12*B9)+tp_wB*(2/12*C8+10/12*C9)+tp_wC*(2/12*D8+10/12*D9)</f>
-        <v>21.7315219206479</v>
+        <v>21.731521920648</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>505</v>
@@ -45396,7 +45396,7 @@
       </c>
       <c r="B43" s="17" t="n">
         <f aca="false">B40/px-1</f>
-        <v>0.659305957903009</v>
+        <v>0.65930595790301</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>516</v>
@@ -45417,7 +45417,7 @@
       </c>
       <c r="B45" s="17" t="n">
         <f aca="false">B35/cons_feps-1</f>
-        <v>0.675581142218257</v>
+        <v>0.675581142218258</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>519</v>
@@ -45553,7 +45553,7 @@
       </c>
       <c r="B56" s="20" t="n">
         <f aca="false">px/PL!F14</f>
-        <v>8.45101282409093</v>
+        <v>8.45101282409092</v>
       </c>
       <c r="C56" s="20" t="n">
         <f aca="false">px/PL!F27</f>
@@ -45570,11 +45570,11 @@
       </c>
       <c r="B57" s="20" t="n">
         <f aca="false">px/PL!G14</f>
-        <v>6.79740418686067</v>
+        <v>6.79740418686066</v>
       </c>
       <c r="C57" s="20" t="n">
         <f aca="false">px/PL!G27</f>
-        <v>9.9410176991414</v>
+        <v>9.94101769914139</v>
       </c>
       <c r="D57" s="20" t="n">
         <f aca="false">px/PL!G40</f>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="B58" s="18" t="n">
         <f aca="false">0.2*PL!D27+0.8*PL!E27</f>
-        <v>17.1829058420002</v>
+        <v>17.1829058420003</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45764,7 +45764,7 @@
       </c>
       <c r="F71" s="35" t="n">
         <f aca="false">E71/px-1</f>
-        <v>-0.0204132464867003</v>
+        <v>-0.0204132464866992</v>
       </c>
       <c r="G71" s="34" t="n">
         <f aca="false">px/C71</f>
@@ -45789,11 +45789,11 @@
       </c>
       <c r="E72" s="30" t="n">
         <f aca="false">C72*D72</f>
-        <v>227.156881418962</v>
+        <v>227.156881418963</v>
       </c>
       <c r="F72" s="35" t="n">
         <f aca="false">E72/px-1</f>
-        <v>-0.110931970962965</v>
+        <v>-0.110931970962964</v>
       </c>
       <c r="G72" s="34" t="n">
         <f aca="false">px/C72</f>
@@ -45822,7 +45822,7 @@
       </c>
       <c r="F73" s="35" t="n">
         <f aca="false">E73/px-1</f>
-        <v>-0.258076338723809</v>
+        <v>-0.258076338723808</v>
       </c>
       <c r="G73" s="34" t="n">
         <f aca="false">px/C73</f>
@@ -45857,7 +45857,7 @@
       </c>
       <c r="B77" s="20" t="n">
         <f aca="false">px*A77/PL!F14</f>
-        <v>8.45101282409093</v>
+        <v>8.45101282409092</v>
       </c>
       <c r="C77" s="20" t="n">
         <f aca="false">px*A77/PL!F27</f>
@@ -45878,7 +45878,7 @@
       </c>
       <c r="B78" s="20" t="n">
         <f aca="false">px*A78/PL!F14</f>
-        <v>9.29611410650002</v>
+        <v>9.29611410650001</v>
       </c>
       <c r="C78" s="20" t="n">
         <f aca="false">px*A78/PL!F27</f>
@@ -45941,11 +45941,11 @@
       </c>
       <c r="B81" s="20" t="n">
         <f aca="false">px*A81/PL!F14</f>
-        <v>16.9020256481819</v>
+        <v>16.9020256481818</v>
       </c>
       <c r="C81" s="20" t="n">
         <f aca="false">px*A81/PL!F27</f>
-        <v>24.3265377821939</v>
+        <v>24.3265377821938</v>
       </c>
       <c r="D81" s="20" t="n">
         <f aca="false">px*A81/PL!F40</f>
@@ -46259,11 +46259,11 @@
       </c>
       <c r="F113" s="22" t="n">
         <f aca="false">C113*E113</f>
-        <v>217.97314611407</v>
+        <v>217.973146114071</v>
       </c>
       <c r="G113" s="17" t="n">
         <f aca="false">F113/px-1</f>
-        <v>-0.146876140453736</v>
+        <v>-0.146876140453735</v>
       </c>
       <c r="H113" s="18" t="n">
         <f aca="false">px/E113</f>
@@ -46290,11 +46290,11 @@
       </c>
       <c r="F114" s="22" t="n">
         <f aca="false">C114*E114</f>
-        <v>227.156881418962</v>
+        <v>227.156881418963</v>
       </c>
       <c r="G114" s="17" t="n">
         <f aca="false">F114/px-1</f>
-        <v>-0.110931970962965</v>
+        <v>-0.110931970962964</v>
       </c>
       <c r="H114" s="18" t="n">
         <f aca="false">px/E114</f>
@@ -46325,7 +46325,7 @@
       </c>
       <c r="G115" s="17" t="n">
         <f aca="false">F115/px-1</f>
-        <v>0.387885075031411</v>
+        <v>0.387885075031413</v>
       </c>
       <c r="H115" s="18" t="n">
         <f aca="false">px/E115</f>
@@ -46523,7 +46523,7 @@
       </c>
       <c r="F7" s="17" t="n">
         <f aca="false">E7/B7-1</f>
-        <v>0.0523365263923441</v>
+        <v>0.0523365263923448</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">PL!E152</f>
@@ -46531,7 +46531,7 @@
       </c>
       <c r="H7" s="17" t="n">
         <f aca="false">G7/B7-1</f>
-        <v>-0.0279504883454345</v>
+        <v>-0.0279504883454337</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>621</v>
@@ -46551,7 +46551,7 @@
       </c>
       <c r="D8" s="17" t="n">
         <f aca="false">C8/B8-1</f>
-        <v>0.377620369149555</v>
+        <v>0.377620369149556</v>
       </c>
       <c r="E8" s="23" t="n">
         <f aca="false">PL!E131</f>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="F8" s="17" t="n">
         <f aca="false">E8/B8-1</f>
-        <v>0.250321344146716</v>
+        <v>0.250321344146718</v>
       </c>
       <c r="G8" s="23" t="n">
         <f aca="false">PL!E169</f>
@@ -46567,7 +46567,7 @@
       </c>
       <c r="H8" s="17" t="n">
         <f aca="false">G8/B8-1</f>
-        <v>0.0873485473896711</v>
+        <v>0.0873485473896725</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>621</v>
@@ -46598,7 +46598,7 @@
       </c>
       <c r="F9" s="17" t="n">
         <f aca="false">E9/B9-1</f>
-        <v>-0.0833714309087569</v>
+        <v>-0.0833714309087562</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">PL!F152</f>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="H9" s="17" t="n">
         <f aca="false">G9/B9-1</f>
-        <v>-0.279883934832851</v>
+        <v>-0.27988393483285</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>621</v>
@@ -46626,15 +46626,15 @@
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">C10/B10-1</f>
-        <v>0.457717581016162</v>
+        <v>0.457717581016164</v>
       </c>
       <c r="E10" s="23" t="n">
         <f aca="false">PL!F131</f>
-        <v>21.0058662919979</v>
+        <v>21.005866291998</v>
       </c>
       <c r="F10" s="17" t="n">
         <f aca="false">E10/B10-1</f>
-        <v>0.0128190111860143</v>
+        <v>0.0128190111860154</v>
       </c>
       <c r="G10" s="23" t="n">
         <f aca="false">PL!F169</f>
@@ -46642,7 +46642,7 @@
       </c>
       <c r="H10" s="17" t="n">
         <f aca="false">G10/B10-1</f>
-        <v>-0.339504164466702</v>
+        <v>-0.339504164466701</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>621</v>
@@ -46659,31 +46659,31 @@
       </c>
       <c r="B12" s="22" t="n">
         <f aca="false">d_pmk26</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="C12" s="22" t="n">
         <f aca="false">PL!D67</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="D12" s="17" t="n">
         <f aca="false">C12/B12-1</f>
-        <v>-3.5527136788005E-015</v>
+        <v>4.66293670342566E-015</v>
       </c>
       <c r="E12" s="22" t="n">
         <f aca="false">PL!D105</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="F12" s="17" t="n">
         <f aca="false">E12/B12-1</f>
-        <v>-3.5527136788005E-015</v>
+        <v>4.66293670342566E-015</v>
       </c>
       <c r="G12" s="22" t="n">
         <f aca="false">PL!D143</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="H12" s="17" t="n">
         <f aca="false">G12/B12-1</f>
-        <v>-3.5527136788005E-015</v>
+        <v>4.66293670342566E-015</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>630</v>
@@ -46773,15 +46773,15 @@
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">PL!D71+d_sh26</f>
-        <v>0.759815255723818</v>
+        <v>0.759815255723819</v>
       </c>
       <c r="E15" s="17" t="n">
         <f aca="false">PL!D109+d_sh26</f>
-        <v>0.759815255723818</v>
+        <v>0.759815255723819</v>
       </c>
       <c r="G15" s="17" t="n">
         <f aca="false">PL!D147+d_sh26</f>
-        <v>0.759815255723818</v>
+        <v>0.759815255723819</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>636</v>
@@ -46796,15 +46796,15 @@
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">PL!E71+d_sh27</f>
-        <v>0.748245990386684</v>
+        <v>0.748245990386685</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">PL!E109+d_sh27</f>
-        <v>0.73063165875398</v>
+        <v>0.730631658753981</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">PL!E147+d_sh27</f>
-        <v>0.704210161304923</v>
+        <v>0.704210161304924</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>636</v>
@@ -46819,15 +46819,15 @@
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">PL!F71+d_sh28</f>
-        <v>0.73667672504955</v>
+        <v>0.736676725049551</v>
       </c>
       <c r="E17" s="17" t="n">
         <f aca="false">PL!F109+d_sh28</f>
-        <v>0.701448061784141</v>
+        <v>0.701448061784142</v>
       </c>
       <c r="G17" s="17" t="n">
         <f aca="false">PL!F147+d_sh28</f>
-        <v>0.666219398518732</v>
+        <v>0.666219398518733</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>636</v>
@@ -46869,27 +46869,27 @@
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">d_sh26</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="D19" s="17" t="n">
         <f aca="false">C19-B19</f>
-        <v>-0.041328060603228</v>
+        <v>-0.041328060603227</v>
       </c>
       <c r="E19" s="17" t="n">
         <f aca="false">d_sh26</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="F19" s="17" t="n">
         <f aca="false">E19-B19</f>
-        <v>-0.041328060603228</v>
+        <v>-0.041328060603227</v>
       </c>
       <c r="G19" s="17" t="n">
         <f aca="false">d_sh26</f>
-        <v>0.583671939396772</v>
+        <v>0.583671939396773</v>
       </c>
       <c r="H19" s="17" t="n">
         <f aca="false">G19-B19</f>
-        <v>-0.041328060603228</v>
+        <v>-0.041328060603227</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>641</v>
@@ -46908,7 +46908,7 @@
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">PL!E109/d_sh27</f>
-        <v>0.317668204810377</v>
+        <v>0.317668204810376</v>
       </c>
       <c r="G20" s="18" t="n">
         <f aca="false">PL!E147/d_sh27</f>
@@ -46935,7 +46935,7 @@
       </c>
       <c r="G21" s="21" t="n">
         <f aca="false">PL!E155</f>
-        <v>99.8145459186591</v>
+        <v>99.8145459186593</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>56</v>
@@ -46986,7 +46986,7 @@
       </c>
       <c r="D24" s="17" t="n">
         <f aca="false">C24-B24</f>
-        <v>0.0320132857032367</v>
+        <v>0.0320132857032368</v>
       </c>
       <c r="E24" s="17" t="n">
         <f aca="false">PL!E122</f>
@@ -46994,7 +46994,7 @@
       </c>
       <c r="F24" s="17" t="n">
         <f aca="false">E24-B24</f>
-        <v>0.0238352393738693</v>
+        <v>0.0238352393738694</v>
       </c>
       <c r="G24" s="17" t="n">
         <f aca="false">PL!E160</f>
@@ -47025,15 +47025,15 @@
       </c>
       <c r="D25" s="17" t="n">
         <f aca="false">C25-B25</f>
-        <v>0.024203481323286</v>
+        <v>0.0242034813232861</v>
       </c>
       <c r="E25" s="17" t="n">
         <f aca="false">PL!E126</f>
-        <v>0.170481498867934</v>
+        <v>0.170481498867935</v>
       </c>
       <c r="F25" s="17" t="n">
         <f aca="false">E25-B25</f>
-        <v>0.0148357102031526</v>
+        <v>0.0148357102031527</v>
       </c>
       <c r="G25" s="17" t="n">
         <f aca="false">PL!E164</f>
@@ -47041,7 +47041,7 @@
       </c>
       <c r="H25" s="17" t="n">
         <f aca="false">G25-B25</f>
-        <v>0.00325481056320284</v>
+        <v>0.00325481056320295</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>656</v>
@@ -47098,11 +47098,11 @@
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">Val!B35</f>
-        <v>21.7315219206479</v>
+        <v>21.731521920648</v>
       </c>
       <c r="D30" s="17" t="n">
         <f aca="false">C30/B30-1</f>
-        <v>0.675581142218257</v>
+        <v>0.675581142218258</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>664</v>
@@ -47125,7 +47125,7 @@
       </c>
       <c r="D31" s="17" t="n">
         <f aca="false">C31/B31-1</f>
-        <v>0.349093626871022</v>
+        <v>0.349093626871023</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>667</v>
@@ -47148,7 +47148,7 @@
       </c>
       <c r="D32" s="17" t="n">
         <f aca="false">C32/B32-1</f>
-        <v>0.68389040180677</v>
+        <v>0.683890401806771</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>39</v>
@@ -47265,7 +47265,7 @@
       </c>
       <c r="K4" s="18" t="n">
         <f aca="false">PL!F131</f>
-        <v>21.0058662919979</v>
+        <v>21.005866291998</v>
       </c>
       <c r="L4" s="17" t="n">
         <f aca="false">K4/K$4-1</f>
@@ -47313,7 +47313,7 @@
       </c>
       <c r="K5" s="18" t="n">
         <f aca="false">F83</f>
-        <v>17.9055568803382</v>
+        <v>17.9055568803383</v>
       </c>
       <c r="L5" s="17" t="n">
         <f aca="false">K5/K$4-1</f>
@@ -47341,11 +47341,11 @@
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">E121</f>
-        <v>20.0739143470758</v>
+        <v>20.0739143470759</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">F6/F$4-1</f>
-        <v>0.0710476405855849</v>
+        <v>0.0710476405855847</v>
       </c>
       <c r="H6" s="22" t="n">
         <f aca="false">F104</f>
@@ -47413,7 +47413,7 @@
       </c>
       <c r="L7" s="17" t="n">
         <f aca="false">K7/K$4-1</f>
-        <v>-0.0314511345723139</v>
+        <v>-0.031451134572314</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47441,7 +47441,7 @@
       </c>
       <c r="G8" s="17" t="n">
         <f aca="false">F8/F$4-1</f>
-        <v>0.00683150390246046</v>
+        <v>0.00683150390246001</v>
       </c>
       <c r="H8" s="22" t="n">
         <f aca="false">F180</f>
@@ -47449,7 +47449,7 @@
       </c>
       <c r="I8" s="22" t="n">
         <f aca="false">F177</f>
-        <v>183.118420617887</v>
+        <v>183.118420617888</v>
       </c>
       <c r="J8" s="17" t="n">
         <f aca="false">F188</f>
@@ -47461,7 +47461,7 @@
       </c>
       <c r="L8" s="17" t="n">
         <f aca="false">K8/K$4-1</f>
-        <v>0.0134406792582233</v>
+        <v>0.0134406792582231</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47485,7 +47485,7 @@
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">E235</f>
-        <v>16.0791221521261</v>
+        <v>16.0791221521262</v>
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">F9/F$4-1</f>
@@ -47505,7 +47505,7 @@
       </c>
       <c r="K9" s="18" t="n">
         <f aca="false">F235</f>
-        <v>17.9178583987181</v>
+        <v>17.9178583987182</v>
       </c>
       <c r="L9" s="17" t="n">
         <f aca="false">K9/K$4-1</f>
@@ -47521,11 +47521,11 @@
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">E256</f>
-        <v>338.984721569607</v>
+        <v>338.984721569608</v>
       </c>
       <c r="D10" s="22" t="n">
         <f aca="false">E253</f>
-        <v>187.796465840607</v>
+        <v>187.796465840608</v>
       </c>
       <c r="E10" s="17" t="n">
         <f aca="false">E264</f>
@@ -47585,7 +47585,7 @@
       </c>
       <c r="G11" s="17" t="n">
         <f aca="false">F11/F$4-1</f>
-        <v>-0.0436886695794363</v>
+        <v>-0.0436886695794365</v>
       </c>
       <c r="H11" s="22" t="n">
         <f aca="false">F294</f>
@@ -47605,7 +47605,7 @@
       </c>
       <c r="L11" s="17" t="n">
         <f aca="false">K11/K$4-1</f>
-        <v>-0.0483674867824453</v>
+        <v>-0.0483674867824454</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47653,7 +47653,7 @@
       </c>
       <c r="L12" s="17" t="n">
         <f aca="false">K12/K$4-1</f>
-        <v>0.0483674867824457</v>
+        <v>0.0483674867824455</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47701,7 +47701,7 @@
       </c>
       <c r="L13" s="17" t="n">
         <f aca="false">K13/K$4-1</f>
-        <v>-0.0430209031499647</v>
+        <v>-0.0430209031499645</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47729,7 +47729,7 @@
       </c>
       <c r="G14" s="17" t="n">
         <f aca="false">F14/F$4-1</f>
-        <v>0.0279685507231588</v>
+        <v>0.0279685507231586</v>
       </c>
       <c r="H14" s="22" t="n">
         <f aca="false">F408</f>
@@ -47749,7 +47749,7 @@
       </c>
       <c r="L14" s="17" t="n">
         <f aca="false">K14/K$4-1</f>
-        <v>0.0430209031499647</v>
+        <v>0.0430209031499644</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47777,7 +47777,7 @@
       </c>
       <c r="G15" s="17" t="n">
         <f aca="false">F15/F$4-1</f>
-        <v>-0.0210954030680264</v>
+        <v>-0.0210954030680267</v>
       </c>
       <c r="H15" s="22" t="n">
         <f aca="false">F446</f>
@@ -47793,11 +47793,11 @@
       </c>
       <c r="K15" s="18" t="n">
         <f aca="false">F463</f>
-        <v>20.1892135929587</v>
+        <v>20.1892135929588</v>
       </c>
       <c r="L15" s="17" t="n">
         <f aca="false">K15/K$4-1</f>
-        <v>-0.0388773634796622</v>
+        <v>-0.0388773634796621</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47825,7 +47825,7 @@
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">F16/F$4-1</f>
-        <v>0.0105477015340134</v>
+        <v>0.010547701534013</v>
       </c>
       <c r="H16" s="22" t="n">
         <f aca="false">F484</f>
@@ -47869,11 +47869,11 @@
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">E539</f>
-        <v>17.7117081772462</v>
+        <v>17.7117081772463</v>
       </c>
       <c r="G17" s="17" t="n">
         <f aca="false">F17/F$4-1</f>
-        <v>-0.0549883333170957</v>
+        <v>-0.0549883333170959</v>
       </c>
       <c r="H17" s="22" t="n">
         <f aca="false">F522</f>
@@ -47889,11 +47889,11 @@
       </c>
       <c r="K17" s="18" t="n">
         <f aca="false">F539</f>
-        <v>19.8817996699718</v>
+        <v>19.8817996699719</v>
       </c>
       <c r="L17" s="17" t="n">
         <f aca="false">K17/K$4-1</f>
-        <v>-0.0535120335624676</v>
+        <v>-0.0535120335624674</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47921,7 +47921,7 @@
       </c>
       <c r="G18" s="17" t="n">
         <f aca="false">F18/F$4-1</f>
-        <v>-0.0603315430165827</v>
+        <v>-0.0603315430165828</v>
       </c>
       <c r="H18" s="22" t="n">
         <f aca="false">F560</f>
@@ -47941,7 +47941,7 @@
       </c>
       <c r="L18" s="17" t="n">
         <f aca="false">K18/K$4-1</f>
-        <v>-0.0730650542163649</v>
+        <v>-0.0730650542163648</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47969,7 +47969,7 @@
       </c>
       <c r="G19" s="17" t="n">
         <f aca="false">F19/F$4-1</f>
-        <v>-0.0394736842105264</v>
+        <v>-0.0394736842105263</v>
       </c>
       <c r="H19" s="22" t="n">
         <f aca="false">F598</f>
@@ -47989,7 +47989,7 @@
       </c>
       <c r="L19" s="17" t="n">
         <f aca="false">K19/K$4-1</f>
-        <v>-0.0394736842105266</v>
+        <v>-0.0394736842105263</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48034,7 +48034,7 @@
       </c>
       <c r="L20" s="17" t="n">
         <f aca="false">K20/K$4-1</f>
-        <v>0.0263157894736841</v>
+        <v>0.0263157894736843</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48220,7 +48220,7 @@
       </c>
       <c r="C30" s="18" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
-        <v>379.34441737238</v>
+        <v>379.344417372381</v>
       </c>
       <c r="D30" s="18" t="n">
         <f aca="false">Val!B36</f>
@@ -48244,7 +48244,7 @@
       </c>
       <c r="C31" s="18" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>336.322720301352</v>
+        <v>336.322720301353</v>
       </c>
       <c r="D31" s="18" t="n">
         <f aca="false">Val!B36</f>
@@ -48256,7 +48256,7 @@
       </c>
       <c r="F31" s="17" t="n">
         <f aca="false">E31/E$28-1</f>
-        <v>0.0207333692315606</v>
+        <v>0.0207333692315603</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48268,7 +48268,7 @@
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>308.028933605496</v>
+        <v>308.028933605497</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">Val!B36</f>
@@ -48280,7 +48280,7 @@
       </c>
       <c r="F32" s="17" t="n">
         <f aca="false">E32/E$28-1</f>
-        <v>-0.012635669989352</v>
+        <v>-0.0126356699893518</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48297,11 +48297,11 @@
       </c>
       <c r="E33" s="18" t="n">
         <f aca="false">0.3*C33+(1-0.3)*D33</f>
-        <v>466.036626853642</v>
+        <v>466.036626853643</v>
       </c>
       <c r="F33" s="17" t="n">
         <f aca="false">E33/E$28-1</f>
-        <v>0.0992656901692579</v>
+        <v>0.0992656901692577</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48318,11 +48318,11 @@
       </c>
       <c r="E34" s="18" t="n">
         <f aca="false">0.7*C34+(1-0.7)*D34</f>
-        <v>381.868717634795</v>
+        <v>381.868717634796</v>
       </c>
       <c r="F34" s="17" t="n">
         <f aca="false">E34/E$28-1</f>
-        <v>-0.0992656901692578</v>
+        <v>-0.0992656901692579</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48379,7 +48379,7 @@
       </c>
       <c r="D53" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E53" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -48475,7 +48475,7 @@
       </c>
       <c r="D57" s="23" t="n">
         <f aca="false">D55*D56/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E57" s="23" t="n">
         <f aca="false">E55*E56/1000</f>
@@ -48570,7 +48570,7 @@
       </c>
       <c r="F61" s="17" t="n">
         <f aca="false">$D$59*F60</f>
-        <v>0.140914653061636</v>
+        <v>0.140914653061637</v>
       </c>
       <c r="G61" s="17" t="n">
         <f aca="false">$D$59*G60</f>
@@ -48602,7 +48602,7 @@
       </c>
       <c r="G62" s="22" t="n">
         <f aca="false">G58*G61</f>
-        <v>155.590145386411</v>
+        <v>155.590145386412</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48725,7 +48725,7 @@
       </c>
       <c r="E67" s="17" t="n">
         <f aca="false">E66/D66-1</f>
-        <v>0.336007090846017</v>
+        <v>0.336007090846018</v>
       </c>
       <c r="F67" s="17" t="n">
         <f aca="false">F66/E66-1</f>
@@ -48785,11 +48785,11 @@
       </c>
       <c r="D69" s="21" t="n">
         <f aca="false">D63/fx/D55*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E69" s="21" t="n">
         <f aca="false">E63/fx/E55*1000</f>
-        <v>99.8145459186591</v>
+        <v>99.8145459186593</v>
       </c>
       <c r="F69" s="21" t="n">
         <f aca="false">F63/fx/F55*1000</f>
@@ -48868,11 +48868,11 @@
       </c>
       <c r="F73" s="22" t="n">
         <f aca="false">F63*F72+F65*$D$71</f>
-        <v>82.2778549086068</v>
+        <v>82.2778549086069</v>
       </c>
       <c r="G73" s="22" t="n">
         <f aca="false">G63*G72+G65*$D$71</f>
-        <v>93.0598285915487</v>
+        <v>93.0598285915488</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48976,11 +48976,11 @@
       </c>
       <c r="E77" s="22" t="n">
         <f aca="false">E73-E76</f>
-        <v>46.4914838243801</v>
+        <v>46.4914838243802</v>
       </c>
       <c r="F77" s="22" t="n">
         <f aca="false">F73-F76</f>
-        <v>49.9565296008124</v>
+        <v>49.9565296008125</v>
       </c>
       <c r="G77" s="22" t="n">
         <f aca="false">G73-G76</f>
@@ -49092,15 +49092,15 @@
       </c>
       <c r="F81" s="22" t="n">
         <f aca="false">(F77+F79)*F80</f>
-        <v>40.6269624966174</v>
+        <v>40.6269624966175</v>
       </c>
       <c r="G81" s="22" t="n">
         <f aca="false">(G77+G79)*G80</f>
-        <v>46.8895478430426</v>
+        <v>46.8895478430427</v>
       </c>
       <c r="H81" s="24" t="n">
         <f aca="false">H66*H85</f>
-        <v>46.9654950723429</v>
+        <v>46.965495072343</v>
       </c>
       <c r="I81" s="24" t="n">
         <f aca="false">I66*I85</f>
@@ -49108,7 +49108,7 @@
       </c>
       <c r="J81" s="24" t="n">
         <f aca="false">J66*J85</f>
-        <v>42.9872100839171</v>
+        <v>42.9872100839172</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49172,7 +49172,7 @@
       </c>
       <c r="F83" s="23" t="n">
         <f aca="false">F81/F82</f>
-        <v>17.9055568803382</v>
+        <v>17.9055568803383</v>
       </c>
       <c r="G83" s="23" t="n">
         <f aca="false">G81/G82</f>
@@ -49184,11 +49184,11 @@
       </c>
       <c r="I83" s="29" t="n">
         <f aca="false">I81/I82</f>
-        <v>20.1216777439503</v>
+        <v>20.1216777439504</v>
       </c>
       <c r="J83" s="29" t="n">
         <f aca="false">J81/J82</f>
-        <v>18.9457908734553</v>
+        <v>18.9457908734554</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49204,15 +49204,15 @@
       </c>
       <c r="E84" s="17" t="n">
         <f aca="false">E83/D83-1</f>
-        <v>0.529878567211852</v>
+        <v>0.529878567211854</v>
       </c>
       <c r="F84" s="17" t="n">
         <f aca="false">F83/E83-1</f>
-        <v>0.0693127211147595</v>
+        <v>0.06931272111476</v>
       </c>
       <c r="G84" s="17" t="n">
         <f aca="false">G83/F83-1</f>
-        <v>0.154148500443434</v>
+        <v>0.154148500443433</v>
       </c>
       <c r="H84" s="25" t="n">
         <f aca="false">H83/G83-1</f>
@@ -49224,7 +49224,7 @@
       </c>
       <c r="J84" s="25" t="n">
         <f aca="false">J83/I83-1</f>
-        <v>-0.0584388084064473</v>
+        <v>-0.0584388084064474</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49264,7 +49264,7 @@
       </c>
       <c r="J85" s="25" t="n">
         <f aca="false">$G85+(fade_mB-$G85)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49321,7 +49321,7 @@
       </c>
       <c r="D91" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E91" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -49417,7 +49417,7 @@
       </c>
       <c r="D95" s="23" t="n">
         <f aca="false">D93*D94/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E95" s="23" t="n">
         <f aca="false">E93*E94/1000</f>
@@ -49544,7 +49544,7 @@
       </c>
       <c r="G100" s="22" t="n">
         <f aca="false">G96*G99</f>
-        <v>259.316908977352</v>
+        <v>259.316908977353</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49640,11 +49640,11 @@
       </c>
       <c r="H104" s="24" t="n">
         <f aca="false">G104*(1+H105)</f>
-        <v>516.445214595284</v>
+        <v>516.445214595285</v>
       </c>
       <c r="I104" s="24" t="n">
         <f aca="false">H104*(1+I105)</f>
-        <v>565.876466538608</v>
+        <v>565.876466538609</v>
       </c>
       <c r="J104" s="24" t="n">
         <f aca="false">I104*(1+J105)</f>
@@ -49667,7 +49667,7 @@
       </c>
       <c r="E105" s="17" t="n">
         <f aca="false">E104/D104-1</f>
-        <v>0.519920941094846</v>
+        <v>0.519920941094847</v>
       </c>
       <c r="F105" s="17" t="n">
         <f aca="false">F104/E104-1</f>
@@ -49679,11 +49679,11 @@
       </c>
       <c r="H105" s="25" t="n">
         <f aca="false">$G105+(fade_gB-$G105)*1/3</f>
-        <v>0.151428831350722</v>
+        <v>0.151428831350723</v>
       </c>
       <c r="I105" s="25" t="n">
         <f aca="false">$G105+(fade_gB-$G105)*2/3</f>
-        <v>0.0957144156753612</v>
+        <v>0.0957144156753613</v>
       </c>
       <c r="J105" s="25" t="n">
         <f aca="false">$G105+(fade_gB-$G105)*3/3</f>
@@ -49711,11 +49711,11 @@
       </c>
       <c r="F106" s="17" t="n">
         <f aca="false">F101/F104</f>
-        <v>0.580891052405764</v>
+        <v>0.580891052405765</v>
       </c>
       <c r="G106" s="17" t="n">
         <f aca="false">G101/G104</f>
-        <v>0.642393546014067</v>
+        <v>0.642393546014068</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49727,7 +49727,7 @@
       </c>
       <c r="D107" s="21" t="n">
         <f aca="false">D101/fx/D93*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E107" s="21" t="n">
         <f aca="false">E101/fx/E93*1000</f>
@@ -49739,7 +49739,7 @@
       </c>
       <c r="G107" s="21" t="n">
         <f aca="false">G101/fx/G93*1000</f>
-        <v>176.143316327045</v>
+        <v>176.143316327046</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49806,7 +49806,7 @@
       </c>
       <c r="E111" s="22" t="n">
         <f aca="false">E101*E110+E103*$D$109</f>
-        <v>90.8155986690357</v>
+        <v>90.8155986690358</v>
       </c>
       <c r="F111" s="22" t="n">
         <f aca="false">F101*F110+F103*$D$109</f>
@@ -49870,7 +49870,7 @@
       </c>
       <c r="G113" s="22" t="n">
         <f aca="false">F113*(1+MAX(0,phi*G105))</f>
-        <v>43.4818970646012</v>
+        <v>43.4818970646013</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49898,7 +49898,7 @@
       </c>
       <c r="G114" s="22" t="n">
         <f aca="false">G113+0*G104</f>
-        <v>43.4818970646012</v>
+        <v>43.4818970646013</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49922,11 +49922,11 @@
       </c>
       <c r="F115" s="22" t="n">
         <f aca="false">F111-F114</f>
-        <v>68.5466672189332</v>
+        <v>68.5466672189333</v>
       </c>
       <c r="G115" s="22" t="n">
         <f aca="false">G111-G114</f>
-        <v>88.415806199475</v>
+        <v>88.4158061994752</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50038,19 +50038,19 @@
       </c>
       <c r="G119" s="22" t="n">
         <f aca="false">(G115+G117)*G118</f>
-        <v>69.856012711601</v>
+        <v>69.8560127116011</v>
       </c>
       <c r="H119" s="24" t="n">
         <f aca="false">H104*H123</f>
-        <v>72.0602320200804</v>
+        <v>72.0602320200805</v>
       </c>
       <c r="I119" s="24" t="n">
         <f aca="false">I104*I123</f>
-        <v>69.7819279180883</v>
+        <v>69.7819279180884</v>
       </c>
       <c r="J119" s="24" t="n">
         <f aca="false">J104*J123</f>
-        <v>63.0306776474579</v>
+        <v>63.030677647458</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50110,7 +50110,7 @@
       </c>
       <c r="E121" s="23" t="n">
         <f aca="false">E119/E120</f>
-        <v>20.0739143470758</v>
+        <v>20.0739143470759</v>
       </c>
       <c r="F121" s="23" t="n">
         <f aca="false">F119/F120</f>
@@ -50118,7 +50118,7 @@
       </c>
       <c r="G121" s="23" t="n">
         <f aca="false">G119/G120</f>
-        <v>30.7877018653645</v>
+        <v>30.7877018653646</v>
       </c>
       <c r="H121" s="29" t="n">
         <f aca="false">H119/H120</f>
@@ -50126,7 +50126,7 @@
       </c>
       <c r="I121" s="29" t="n">
         <f aca="false">I119/I120</f>
-        <v>30.7550504092208</v>
+        <v>30.7550504092209</v>
       </c>
       <c r="J121" s="29" t="n">
         <f aca="false">J119/J120</f>
@@ -50146,7 +50146,7 @@
       </c>
       <c r="E122" s="17" t="n">
         <f aca="false">E121/D121-1</f>
-        <v>0.834027857903081</v>
+        <v>0.834027857903083</v>
       </c>
       <c r="F122" s="17" t="n">
         <f aca="false">F121/E121-1</f>
@@ -50162,11 +50162,11 @@
       </c>
       <c r="I122" s="25" t="n">
         <f aca="false">I121/H121-1</f>
-        <v>-0.0316166634234145</v>
+        <v>-0.0316166634234149</v>
       </c>
       <c r="J122" s="25" t="n">
         <f aca="false">J121/I121-1</f>
-        <v>-0.0967478324553494</v>
+        <v>-0.0967478324553492</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50206,7 +50206,7 @@
       </c>
       <c r="J123" s="25" t="n">
         <f aca="false">$G123+(fade_mB-$G123)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50263,7 +50263,7 @@
       </c>
       <c r="D129" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E129" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -50359,7 +50359,7 @@
       </c>
       <c r="D133" s="23" t="n">
         <f aca="false">D131*D132/1000</f>
-        <v>8.89182445598429</v>
+        <v>8.89182445598428</v>
       </c>
       <c r="E133" s="23" t="n">
         <f aca="false">E131*E132/1000</f>
@@ -50609,11 +50609,11 @@
       </c>
       <c r="E143" s="17" t="n">
         <f aca="false">E142/D142-1</f>
-        <v>0.436675724666429</v>
+        <v>0.43667572466643</v>
       </c>
       <c r="F143" s="17" t="n">
         <f aca="false">F142/E142-1</f>
-        <v>0.0732059346118659</v>
+        <v>0.0732059346118661</v>
       </c>
       <c r="G143" s="17" t="n">
         <f aca="false">G142/F142-1</f>
@@ -50649,7 +50649,7 @@
       </c>
       <c r="E144" s="17" t="n">
         <f aca="false">E139/E142</f>
-        <v>0.505316343975247</v>
+        <v>0.505316343975248</v>
       </c>
       <c r="F144" s="17" t="n">
         <f aca="false">F139/F142</f>
@@ -50669,7 +50669,7 @@
       </c>
       <c r="D145" s="21" t="n">
         <f aca="false">D139/fx/D131*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E145" s="21" t="n">
         <f aca="false">E139/fx/E131*1000</f>
@@ -50748,11 +50748,11 @@
       </c>
       <c r="E149" s="22" t="n">
         <f aca="false">E139*E148+E141*$D$147</f>
-        <v>84.8480198237189</v>
+        <v>84.848019823719</v>
       </c>
       <c r="F149" s="22" t="n">
         <f aca="false">F139*F148+F141*$D$147</f>
-        <v>91.8432660018135</v>
+        <v>91.8432660018136</v>
       </c>
       <c r="G149" s="22" t="n">
         <f aca="false">G139*G148+G141*$D$147</f>
@@ -50860,15 +50860,15 @@
       </c>
       <c r="E153" s="22" t="n">
         <f aca="false">E149-E152</f>
-        <v>51.9315679208094</v>
+        <v>51.9315679208095</v>
       </c>
       <c r="F153" s="22" t="n">
         <f aca="false">F149-F152</f>
-        <v>57.2400383609427</v>
+        <v>57.2400383609428</v>
       </c>
       <c r="G153" s="22" t="n">
         <f aca="false">G149-G152</f>
-        <v>67.4444766388759</v>
+        <v>67.444476638876</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50888,7 +50888,7 @@
       </c>
       <c r="E154" s="17" t="n">
         <f aca="false">E153/E142</f>
-        <v>0.169918607489008</v>
+        <v>0.169918607489009</v>
       </c>
       <c r="F154" s="17" t="n">
         <f aca="false">F153/F142</f>
@@ -50980,11 +50980,11 @@
       </c>
       <c r="G157" s="22" t="n">
         <f aca="false">(G153+G155)*G156</f>
-        <v>53.9178022455457</v>
+        <v>53.9178022455458</v>
       </c>
       <c r="H157" s="24" t="n">
         <f aca="false">H142*H161</f>
-        <v>53.8544840820874</v>
+        <v>53.8544840820875</v>
       </c>
       <c r="I157" s="24" t="n">
         <f aca="false">I142*I161</f>
@@ -51060,11 +51060,11 @@
       </c>
       <c r="G159" s="23" t="n">
         <f aca="false">G157/G158</f>
-        <v>23.7632403616398</v>
+        <v>23.7632403616399</v>
       </c>
       <c r="H159" s="29" t="n">
         <f aca="false">H157/H158</f>
-        <v>23.7353340918207</v>
+        <v>23.7353340918208</v>
       </c>
       <c r="I159" s="29" t="n">
         <f aca="false">I157/I158</f>
@@ -51088,27 +51088,27 @@
       </c>
       <c r="E160" s="17" t="n">
         <f aca="false">E159/D159-1</f>
-        <v>0.696360284221788</v>
+        <v>0.69636028422179</v>
       </c>
       <c r="F160" s="17" t="n">
         <f aca="false">F159/E159-1</f>
-        <v>0.095766196758444</v>
+        <v>0.0957661967584436</v>
       </c>
       <c r="G160" s="17" t="n">
         <f aca="false">G159/F159-1</f>
-        <v>0.168001841179193</v>
+        <v>0.168001841179194</v>
       </c>
       <c r="H160" s="25" t="n">
         <f aca="false">H159/G159-1</f>
-        <v>-0.00117434614953149</v>
+        <v>-0.00117434614953171</v>
       </c>
       <c r="I160" s="25" t="n">
         <f aca="false">I159/H159-1</f>
-        <v>-0.036204397051086</v>
+        <v>-0.0362043970510861</v>
       </c>
       <c r="J160" s="25" t="n">
         <f aca="false">J159/I159-1</f>
-        <v>-0.0727055252023185</v>
+        <v>-0.0727055252023187</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51128,7 +51128,7 @@
       </c>
       <c r="E161" s="17" t="n">
         <f aca="false">E157/E142</f>
-        <v>0.137841585743441</v>
+        <v>0.137841585743442</v>
       </c>
       <c r="F161" s="17" t="n">
         <f aca="false">F157/F142</f>
@@ -51148,7 +51148,7 @@
       </c>
       <c r="J161" s="25" t="n">
         <f aca="false">$G161+(fade_mB-$G161)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51205,7 +51205,7 @@
       </c>
       <c r="D167" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E167" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -51325,7 +51325,7 @@
       </c>
       <c r="D172" s="22" t="n">
         <f aca="false">D171*fx</f>
-        <v>389.368313019944</v>
+        <v>389.368313019943</v>
       </c>
       <c r="E172" s="22" t="n">
         <f aca="false">E171*fx</f>
@@ -51452,7 +51452,7 @@
       </c>
       <c r="F177" s="22" t="n">
         <f aca="false">F176/(1-x_np)</f>
-        <v>183.118420617887</v>
+        <v>183.118420617888</v>
       </c>
       <c r="G177" s="22" t="n">
         <f aca="false">G176/(1-x_np)</f>
@@ -51532,7 +51532,7 @@
       </c>
       <c r="J180" s="24" t="n">
         <f aca="false">I180*(1+J181)</f>
-        <v>501.783851635516</v>
+        <v>501.783851635517</v>
       </c>
       <c r="K180" s="8" t="s">
         <v>446</v>
@@ -51551,7 +51551,7 @@
       </c>
       <c r="E181" s="17" t="n">
         <f aca="false">E180/D180-1</f>
-        <v>0.45342901062027</v>
+        <v>0.453429010620271</v>
       </c>
       <c r="F181" s="17" t="n">
         <f aca="false">F180/E180-1</f>
@@ -51567,7 +51567,7 @@
       </c>
       <c r="I181" s="25" t="n">
         <f aca="false">$G181+(fade_gB-$G181)*2/3</f>
-        <v>0.0827833077174273</v>
+        <v>0.0827833077174274</v>
       </c>
       <c r="J181" s="25" t="n">
         <f aca="false">$G181+(fade_gB-$G181)*3/3</f>
@@ -51591,7 +51591,7 @@
       </c>
       <c r="E182" s="17" t="n">
         <f aca="false">E177/E180</f>
-        <v>0.511018429653678</v>
+        <v>0.511018429653679</v>
       </c>
       <c r="F182" s="17" t="n">
         <f aca="false">F177/F180</f>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="D183" s="21" t="n">
         <f aca="false">D177/fx/D169*1000</f>
-        <v>88.0716581635227</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E183" s="21" t="n">
         <f aca="false">E177/fx/E169*1000</f>
@@ -51623,7 +51623,7 @@
       </c>
       <c r="G183" s="21" t="n">
         <f aca="false">G177/fx/G169*1000</f>
-        <v>143.963287382681</v>
+        <v>143.963287382682</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51694,7 +51694,7 @@
       </c>
       <c r="F187" s="22" t="n">
         <f aca="false">F177*F186+F179*$D$185</f>
-        <v>95.4970098173611</v>
+        <v>95.4970098173612</v>
       </c>
       <c r="G187" s="22" t="n">
         <f aca="false">G177*G186+G179*$D$185</f>
@@ -51810,7 +51810,7 @@
       </c>
       <c r="G191" s="22" t="n">
         <f aca="false">G187-G190</f>
-        <v>74.5409285671242</v>
+        <v>74.5409285671243</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51918,23 +51918,23 @@
       </c>
       <c r="F195" s="22" t="n">
         <f aca="false">(F191+F193)*F194</f>
-        <v>48.3020374379376</v>
+        <v>48.3020374379377</v>
       </c>
       <c r="G195" s="22" t="n">
         <f aca="false">(G191+G193)*G194</f>
-        <v>59.3111057110144</v>
+        <v>59.3111057110145</v>
       </c>
       <c r="H195" s="24" t="n">
         <f aca="false">H180*H199</f>
-        <v>60.4138053361801</v>
+        <v>60.4138053361802</v>
       </c>
       <c r="I195" s="24" t="n">
         <f aca="false">I180*I199</f>
-        <v>58.5450216655266</v>
+        <v>58.5450216655267</v>
       </c>
       <c r="J195" s="24" t="n">
         <f aca="false">J180*J199</f>
-        <v>53.7419826916413</v>
+        <v>53.7419826916414</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52006,7 +52006,7 @@
       </c>
       <c r="H197" s="29" t="n">
         <f aca="false">H195/H196</f>
-        <v>26.6262295118597</v>
+        <v>26.6262295118598</v>
       </c>
       <c r="I197" s="29" t="n">
         <f aca="false">I195/I196</f>
@@ -52014,7 +52014,7 @@
       </c>
       <c r="J197" s="29" t="n">
         <f aca="false">J195/J196</f>
-        <v>23.6857512551536</v>
+        <v>23.6857512551537</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52030,7 +52030,7 @@
       </c>
       <c r="E198" s="17" t="n">
         <f aca="false">E197/D197-1</f>
-        <v>0.72406619126856</v>
+        <v>0.724066191268562</v>
       </c>
       <c r="F198" s="17" t="n">
         <f aca="false">F197/E197-1</f>
@@ -52038,19 +52038,19 @@
       </c>
       <c r="G198" s="17" t="n">
         <f aca="false">G197/F197-1</f>
-        <v>0.2279214057424</v>
+        <v>0.227921405742401</v>
       </c>
       <c r="H198" s="25" t="n">
         <f aca="false">H197/G197-1</f>
-        <v>0.018591790052582</v>
+        <v>0.0185917900525823</v>
       </c>
       <c r="I198" s="25" t="n">
         <f aca="false">I197/H197-1</f>
-        <v>-0.0309330567782373</v>
+        <v>-0.0309330567782375</v>
       </c>
       <c r="J198" s="25" t="n">
         <f aca="false">J197/I197-1</f>
-        <v>-0.0820400921759926</v>
+        <v>-0.0820400921759928</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52090,7 +52090,7 @@
       </c>
       <c r="J199" s="25" t="n">
         <f aca="false">$G199+(fade_mB-$G199)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52147,7 +52147,7 @@
       </c>
       <c r="D205" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E205" s="23" t="n">
         <f aca="false">itc_27*1*mf_lo</f>
@@ -52243,7 +52243,7 @@
       </c>
       <c r="D209" s="23" t="n">
         <f aca="false">D207*D208/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E209" s="23" t="n">
         <f aca="false">E207*E208/1000</f>
@@ -52362,7 +52362,7 @@
       </c>
       <c r="E214" s="22" t="n">
         <f aca="false">E210*E213</f>
-        <v>112.677879504364</v>
+        <v>112.677879504365</v>
       </c>
       <c r="F214" s="22" t="n">
         <f aca="false">F210*F213</f>
@@ -52474,7 +52474,7 @@
       </c>
       <c r="J218" s="24" t="n">
         <f aca="false">I218*(1+J219)</f>
-        <v>430.154549473198</v>
+        <v>430.154549473199</v>
       </c>
       <c r="K218" s="8" t="s">
         <v>446</v>
@@ -52493,11 +52493,11 @@
       </c>
       <c r="E219" s="17" t="n">
         <f aca="false">E218/D218-1</f>
-        <v>0.299224320796252</v>
+        <v>0.299224320796253</v>
       </c>
       <c r="F219" s="17" t="n">
         <f aca="false">F218/E218-1</f>
-        <v>0.0840433228798507</v>
+        <v>0.084043322879851</v>
       </c>
       <c r="G219" s="17" t="n">
         <f aca="false">G218/F218-1</f>
@@ -52541,7 +52541,7 @@
       </c>
       <c r="G220" s="17" t="n">
         <f aca="false">G215/G218</f>
-        <v>0.534813807137846</v>
+        <v>0.534813807137847</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52553,7 +52553,7 @@
       </c>
       <c r="D221" s="21" t="n">
         <f aca="false">D215/fx/D207*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E221" s="21" t="n">
         <f aca="false">E215/fx/E207*1000</f>
@@ -52565,7 +52565,7 @@
       </c>
       <c r="G221" s="21" t="n">
         <f aca="false">G215/fx/G207*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52632,15 +52632,15 @@
       </c>
       <c r="E225" s="22" t="n">
         <f aca="false">E215*E224+E217*$D$223</f>
-        <v>74.9945756837772</v>
+        <v>74.9945756837773</v>
       </c>
       <c r="F225" s="22" t="n">
         <f aca="false">F215*F224+F217*$D$223</f>
-        <v>82.2778549086068</v>
+        <v>82.2778549086069</v>
       </c>
       <c r="G225" s="22" t="n">
         <f aca="false">G215*G224+G217*$D$223</f>
-        <v>96.9436160588014</v>
+        <v>96.9436160588016</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52744,15 +52744,15 @@
       </c>
       <c r="E229" s="22" t="n">
         <f aca="false">E225-E228</f>
-        <v>44.5037607891463</v>
+        <v>44.5037607891464</v>
       </c>
       <c r="F229" s="22" t="n">
         <f aca="false">F225-F228</f>
-        <v>49.9932554332344</v>
+        <v>49.9932554332345</v>
       </c>
       <c r="G229" s="22" t="n">
         <f aca="false">G225-G228</f>
-        <v>61.2508557395911</v>
+        <v>61.2508557395912</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52780,7 +52780,7 @@
       </c>
       <c r="G230" s="17" t="n">
         <f aca="false">G229/G218</f>
-        <v>0.17764233400958</v>
+        <v>0.177642334009581</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52856,7 +52856,7 @@
       </c>
       <c r="E233" s="22" t="n">
         <f aca="false">(E229+E231)*E232</f>
-        <v>36.4828581997512</v>
+        <v>36.4828581997513</v>
       </c>
       <c r="F233" s="22" t="n">
         <f aca="false">(F229+F231)*F232</f>
@@ -52864,19 +52864,19 @@
       </c>
       <c r="G233" s="22" t="n">
         <f aca="false">(G229+G231)*G232</f>
-        <v>49.2106503620892</v>
+        <v>49.2106503620893</v>
       </c>
       <c r="H233" s="24" t="n">
         <f aca="false">H218*H237</f>
-        <v>50.2541737499159</v>
+        <v>50.254173749916</v>
       </c>
       <c r="I233" s="24" t="n">
         <f aca="false">I218*I237</f>
-        <v>49.209478387116</v>
+        <v>49.2094783871161</v>
       </c>
       <c r="J233" s="24" t="n">
         <f aca="false">J218*J237</f>
-        <v>46.0703513617877</v>
+        <v>46.0703513617878</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52936,11 +52936,11 @@
       </c>
       <c r="E235" s="23" t="n">
         <f aca="false">E233/E234</f>
-        <v>16.0791221521261</v>
+        <v>16.0791221521262</v>
       </c>
       <c r="F235" s="23" t="n">
         <f aca="false">F233/F234</f>
-        <v>17.9178583987181</v>
+        <v>17.9178583987182</v>
       </c>
       <c r="G235" s="23" t="n">
         <f aca="false">G233/G234</f>
@@ -52948,7 +52948,7 @@
       </c>
       <c r="H235" s="29" t="n">
         <f aca="false">H233/H234</f>
-        <v>22.1485661555042</v>
+        <v>22.1485661555043</v>
       </c>
       <c r="I235" s="29" t="n">
         <f aca="false">I233/I234</f>
@@ -52972,7 +52972,7 @@
       </c>
       <c r="E236" s="17" t="n">
         <f aca="false">E235/D235-1</f>
-        <v>0.469048709073606</v>
+        <v>0.469048709073608</v>
       </c>
       <c r="F236" s="17" t="n">
         <f aca="false">F235/E235-1</f>
@@ -52984,15 +52984,15 @@
       </c>
       <c r="H236" s="25" t="n">
         <f aca="false">H235/G235-1</f>
-        <v>0.021205234642268</v>
+        <v>0.0212052346422678</v>
       </c>
       <c r="I236" s="25" t="n">
         <f aca="false">I235/H235-1</f>
-        <v>-0.020788230804445</v>
+        <v>-0.0207882308044451</v>
       </c>
       <c r="J236" s="25" t="n">
         <f aca="false">J235/I235-1</f>
-        <v>-0.0637911054580528</v>
+        <v>-0.0637911054580529</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53032,7 +53032,7 @@
       </c>
       <c r="J237" s="25" t="n">
         <f aca="false">$G237+(fade_mB-$G237)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53089,7 +53089,7 @@
       </c>
       <c r="D243" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E243" s="23" t="n">
         <f aca="false">itc_27*1*mf_hi</f>
@@ -53185,7 +53185,7 @@
       </c>
       <c r="D247" s="23" t="n">
         <f aca="false">D245*D246/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E247" s="23" t="n">
         <f aca="false">E245*E246/1000</f>
@@ -53312,7 +53312,7 @@
       </c>
       <c r="G252" s="22" t="n">
         <f aca="false">G248*G251</f>
-        <v>248.944232618258</v>
+        <v>248.944232618259</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53332,7 +53332,7 @@
       </c>
       <c r="E253" s="22" t="n">
         <f aca="false">E252/(1-x_np)</f>
-        <v>187.796465840607</v>
+        <v>187.796465840608</v>
       </c>
       <c r="F253" s="22" t="n">
         <f aca="false">F252/(1-x_np)</f>
@@ -53396,7 +53396,7 @@
       </c>
       <c r="E256" s="22" t="n">
         <f aca="false">E253+E255</f>
-        <v>338.984721569607</v>
+        <v>338.984721569608</v>
       </c>
       <c r="F256" s="22" t="n">
         <f aca="false">F253+F255</f>
@@ -53412,11 +53412,11 @@
       </c>
       <c r="I256" s="24" t="n">
         <f aca="false">H256*(1+I257)</f>
-        <v>536.325063924726</v>
+        <v>536.325063924727</v>
       </c>
       <c r="J256" s="24" t="n">
         <f aca="false">I256*(1+J257)</f>
-        <v>557.778066481715</v>
+        <v>557.778066481716</v>
       </c>
       <c r="K256" s="8" t="s">
         <v>446</v>
@@ -53435,7 +53435,7 @@
       </c>
       <c r="E257" s="17" t="n">
         <f aca="false">E256/D256-1</f>
-        <v>0.593486481194378</v>
+        <v>0.593486481194379</v>
       </c>
       <c r="F257" s="17" t="n">
         <f aca="false">F256/E256-1</f>
@@ -53479,7 +53479,7 @@
       </c>
       <c r="F258" s="17" t="n">
         <f aca="false">F253/F256</f>
-        <v>0.580891052405764</v>
+        <v>0.580891052405765</v>
       </c>
       <c r="G258" s="17" t="n">
         <f aca="false">G253/G256</f>
@@ -53495,7 +53495,7 @@
       </c>
       <c r="D259" s="21" t="n">
         <f aca="false">D253/fx/D245*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E259" s="21" t="n">
         <f aca="false">E253/fx/E245*1000</f>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="G259" s="21" t="n">
         <f aca="false">G253/fx/G245*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53574,7 +53574,7 @@
       </c>
       <c r="E263" s="22" t="n">
         <f aca="false">E253*E262+E255*$D$261</f>
-        <v>96.0892729974552</v>
+        <v>96.0892729974553</v>
       </c>
       <c r="F263" s="22" t="n">
         <f aca="false">F253*F262+F255*$D$261</f>
@@ -53638,7 +53638,7 @@
       </c>
       <c r="G265" s="22" t="n">
         <f aca="false">F265*(1+MAX(0,phi*G257))</f>
-        <v>42.7793311693993</v>
+        <v>42.7793311693994</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53666,7 +53666,7 @@
       </c>
       <c r="G266" s="22" t="n">
         <f aca="false">G265+0*G256</f>
-        <v>42.7793311693993</v>
+        <v>42.7793311693994</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53686,15 +53686,15 @@
       </c>
       <c r="E267" s="22" t="n">
         <f aca="false">E263-E266</f>
-        <v>60.4055450710166</v>
+        <v>60.4055450710167</v>
       </c>
       <c r="F267" s="22" t="n">
         <f aca="false">F263-F266</f>
-        <v>68.438064980124</v>
+        <v>68.4380649801241</v>
       </c>
       <c r="G267" s="22" t="n">
         <f aca="false">G263-G266</f>
-        <v>85.2345846274242</v>
+        <v>85.2345846274243</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53798,7 +53798,7 @@
       </c>
       <c r="E271" s="22" t="n">
         <f aca="false">(E267+E269)*E270</f>
-        <v>48.5682142539726</v>
+        <v>48.5682142539727</v>
       </c>
       <c r="F271" s="22" t="n">
         <f aca="false">(F267+F269)*F270</f>
@@ -53806,15 +53806,15 @@
       </c>
       <c r="G271" s="22" t="n">
         <f aca="false">(G267+G269)*G270</f>
-        <v>67.4382843168424</v>
+        <v>67.4382843168425</v>
       </c>
       <c r="H271" s="24" t="n">
         <f aca="false">H256*H275</f>
-        <v>68.4782555427726</v>
+        <v>68.4782555427727</v>
       </c>
       <c r="I271" s="24" t="n">
         <f aca="false">I256*I275</f>
-        <v>65.8829964364141</v>
+        <v>65.8829964364142</v>
       </c>
       <c r="J271" s="24" t="n">
         <f aca="false">J256*J275</f>
@@ -53890,7 +53890,7 @@
       </c>
       <c r="H273" s="29" t="n">
         <f aca="false">H271/H272</f>
-        <v>30.1804817377016</v>
+        <v>30.1804817377017</v>
       </c>
       <c r="I273" s="29" t="n">
         <f aca="false">I271/I272</f>
@@ -53914,7 +53914,7 @@
       </c>
       <c r="E274" s="17" t="n">
         <f aca="false">E273/D273-1</f>
-        <v>0.955687574179573</v>
+        <v>0.955687574179575</v>
       </c>
       <c r="F274" s="17" t="n">
         <f aca="false">F273/E273-1</f>
@@ -53922,19 +53922,19 @@
       </c>
       <c r="G274" s="17" t="n">
         <f aca="false">G273/F273-1</f>
-        <v>0.233485841632533</v>
+        <v>0.233485841632534</v>
       </c>
       <c r="H274" s="25" t="n">
         <f aca="false">H273/G273-1</f>
-        <v>0.0154210807179522</v>
+        <v>0.015421080717952</v>
       </c>
       <c r="I274" s="25" t="n">
         <f aca="false">I273/H273-1</f>
-        <v>-0.0378990248187244</v>
+        <v>-0.0378990248187247</v>
       </c>
       <c r="J274" s="25" t="n">
         <f aca="false">J273/I273-1</f>
-        <v>-0.0932551590645371</v>
+        <v>-0.093255159064537</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53974,7 +53974,7 @@
       </c>
       <c r="J275" s="25" t="n">
         <f aca="false">$G275+(fade_mB-$G275)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54031,7 +54031,7 @@
       </c>
       <c r="D281" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E281" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -54127,7 +54127,7 @@
       </c>
       <c r="D285" s="23" t="n">
         <f aca="false">D283*D284/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E285" s="23" t="n">
         <f aca="false">E283*E284/1000</f>
@@ -54246,7 +54246,7 @@
       </c>
       <c r="E290" s="22" t="n">
         <f aca="false">E286*E289</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F290" s="22" t="n">
         <f aca="false">F286*F289</f>
@@ -54350,7 +54350,7 @@
       </c>
       <c r="H294" s="24" t="n">
         <f aca="false">G294*(1+H295)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I294" s="24" t="n">
         <f aca="false">H294*(1+I295)</f>
@@ -54358,7 +54358,7 @@
       </c>
       <c r="J294" s="24" t="n">
         <f aca="false">I294*(1+J295)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K294" s="8" t="s">
         <v>446</v>
@@ -54393,7 +54393,7 @@
       </c>
       <c r="I295" s="25" t="n">
         <f aca="false">$G295+(fade_gB-$G295)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J295" s="25" t="n">
         <f aca="false">$G295+(fade_gB-$G295)*3/3</f>
@@ -54417,7 +54417,7 @@
       </c>
       <c r="E296" s="17" t="n">
         <f aca="false">E291/E294</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F296" s="17" t="n">
         <f aca="false">F291/F294</f>
@@ -54437,7 +54437,7 @@
       </c>
       <c r="D297" s="21" t="n">
         <f aca="false">D291/fx/D283*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E297" s="21" t="n">
         <f aca="false">E291/fx/E283*1000</f>
@@ -54449,7 +54449,7 @@
       </c>
       <c r="G297" s="21" t="n">
         <f aca="false">G291/fx/G283*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54552,7 +54552,7 @@
       </c>
       <c r="G302" s="17" t="n">
         <f aca="false">G301/G294</f>
-        <v>0.276556384710644</v>
+        <v>0.276556384710643</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54572,7 +54572,7 @@
       </c>
       <c r="E303" s="22" t="n">
         <f aca="false">D303*(1+MAX(0,phi*E295))</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F303" s="22" t="n">
         <f aca="false">E303*(1+MAX(0,phi*F295))</f>
@@ -54600,7 +54600,7 @@
       </c>
       <c r="E304" s="22" t="n">
         <f aca="false">E303+0*E294</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F304" s="22" t="n">
         <f aca="false">F303+0*F294</f>
@@ -54628,7 +54628,7 @@
       </c>
       <c r="E305" s="22" t="n">
         <f aca="false">E301-E304</f>
-        <v>50.0100685867871</v>
+        <v>50.0100685867872</v>
       </c>
       <c r="F305" s="22" t="n">
         <f aca="false">F301-F304</f>
@@ -54636,7 +54636,7 @@
       </c>
       <c r="G305" s="22" t="n">
         <f aca="false">G301-G304</f>
-        <v>68.8583734381286</v>
+        <v>68.8583734381287</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54740,7 +54740,7 @@
       </c>
       <c r="E309" s="22" t="n">
         <f aca="false">(E305+E307)*E308</f>
-        <v>40.6676521259582</v>
+        <v>40.6676521259583</v>
       </c>
       <c r="F309" s="22" t="n">
         <f aca="false">(F305+F307)*F308</f>
@@ -54748,7 +54748,7 @@
       </c>
       <c r="G309" s="22" t="n">
         <f aca="false">(G305+G307)*G308</f>
-        <v>54.9923638129777</v>
+        <v>54.9923638129778</v>
       </c>
       <c r="H309" s="24" t="n">
         <f aca="false">H294*H313</f>
@@ -54756,7 +54756,7 @@
       </c>
       <c r="I309" s="24" t="n">
         <f aca="false">I294*I313</f>
-        <v>56.1778274060757</v>
+        <v>56.1778274060758</v>
       </c>
       <c r="J309" s="24" t="n">
         <f aca="false">J294*J313</f>
@@ -54832,7 +54832,7 @@
       </c>
       <c r="H311" s="29" t="n">
         <f aca="false">H309/H310</f>
-        <v>25.0571967621891</v>
+        <v>25.0571967621892</v>
       </c>
       <c r="I311" s="29" t="n">
         <f aca="false">I309/I310</f>
@@ -54856,7 +54856,7 @@
       </c>
       <c r="E312" s="17" t="n">
         <f aca="false">E311/D311-1</f>
-        <v>0.637557055688712</v>
+        <v>0.637557055688714</v>
       </c>
       <c r="F312" s="17" t="n">
         <f aca="false">F311/E311-1</f>
@@ -54864,7 +54864,7 @@
       </c>
       <c r="G312" s="17" t="n">
         <f aca="false">G311/F311-1</f>
-        <v>0.212456033256229</v>
+        <v>0.21245603325623</v>
       </c>
       <c r="H312" s="25" t="n">
         <f aca="false">H311/G311-1</f>
@@ -54872,11 +54872,11 @@
       </c>
       <c r="I312" s="25" t="n">
         <f aca="false">I311/H311-1</f>
-        <v>-0.0118885415825153</v>
+        <v>-0.0118885415825151</v>
       </c>
       <c r="J312" s="25" t="n">
         <f aca="false">J311/I311-1</f>
-        <v>-0.0584061867314755</v>
+        <v>-0.0584061867314754</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54916,7 +54916,7 @@
       </c>
       <c r="J313" s="25" t="n">
         <f aca="false">$G313+(fade_mB-$G313)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54973,7 +54973,7 @@
       </c>
       <c r="D319" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E319" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -55069,7 +55069,7 @@
       </c>
       <c r="D323" s="23" t="n">
         <f aca="false">D321*D322/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E323" s="23" t="n">
         <f aca="false">E321*E322/1000</f>
@@ -55188,7 +55188,7 @@
       </c>
       <c r="E328" s="22" t="n">
         <f aca="false">E324*E327</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F328" s="22" t="n">
         <f aca="false">F324*F327</f>
@@ -55292,7 +55292,7 @@
       </c>
       <c r="H332" s="24" t="n">
         <f aca="false">G332*(1+H333)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I332" s="24" t="n">
         <f aca="false">H332*(1+I333)</f>
@@ -55300,7 +55300,7 @@
       </c>
       <c r="J332" s="24" t="n">
         <f aca="false">I332*(1+J333)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K332" s="8" t="s">
         <v>446</v>
@@ -55335,7 +55335,7 @@
       </c>
       <c r="I333" s="25" t="n">
         <f aca="false">$G333+(fade_gB-$G333)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J333" s="25" t="n">
         <f aca="false">$G333+(fade_gB-$G333)*3/3</f>
@@ -55359,7 +55359,7 @@
       </c>
       <c r="E334" s="17" t="n">
         <f aca="false">E329/E332</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F334" s="17" t="n">
         <f aca="false">F329/F332</f>
@@ -55379,7 +55379,7 @@
       </c>
       <c r="D335" s="21" t="n">
         <f aca="false">D329/fx/D321*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E335" s="21" t="n">
         <f aca="false">E329/fx/E321*1000</f>
@@ -55391,7 +55391,7 @@
       </c>
       <c r="G335" s="21" t="n">
         <f aca="false">G329/fx/G321*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="336" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55458,11 +55458,11 @@
       </c>
       <c r="E339" s="22" t="n">
         <f aca="false">E329*E338+E331*$D$337</f>
-        <v>87.9865086839106</v>
+        <v>87.9865086839107</v>
       </c>
       <c r="F339" s="22" t="n">
         <f aca="false">F329*F338+F331*$D$337</f>
-        <v>97.4332264155631</v>
+        <v>97.4332264155632</v>
       </c>
       <c r="G339" s="22" t="n">
         <f aca="false">G329*G338+G331*$D$337</f>
@@ -55514,7 +55514,7 @@
       </c>
       <c r="E341" s="22" t="n">
         <f aca="false">D341*(1+MAX(0,phi*E333))</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F341" s="22" t="n">
         <f aca="false">E341*(1+MAX(0,phi*F333))</f>
@@ -55542,7 +55542,7 @@
       </c>
       <c r="E342" s="22" t="n">
         <f aca="false">E341+0*E332</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F342" s="22" t="n">
         <f aca="false">F341+0*F332</f>
@@ -55574,11 +55574,11 @@
       </c>
       <c r="F343" s="22" t="n">
         <f aca="false">F339-F342</f>
-        <v>62.2456568651416</v>
+        <v>62.2456568651417</v>
       </c>
       <c r="G343" s="22" t="n">
         <f aca="false">G339-G342</f>
-        <v>77.6043783834788</v>
+        <v>77.6043783834789</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55686,11 +55686,11 @@
       </c>
       <c r="F347" s="22" t="n">
         <f aca="false">(F343+F345)*F346</f>
-        <v>49.9666992175076</v>
+        <v>49.9666992175077</v>
       </c>
       <c r="G347" s="22" t="n">
         <f aca="false">(G343+G345)*G346</f>
-        <v>61.6393275714439</v>
+        <v>61.639327571444</v>
       </c>
       <c r="H347" s="24" t="n">
         <f aca="false">H332*H351</f>
@@ -55698,7 +55698,7 @@
       </c>
       <c r="I347" s="24" t="n">
         <f aca="false">I332*I351</f>
-        <v>58.8695796873212</v>
+        <v>58.8695796873213</v>
       </c>
       <c r="J347" s="24" t="n">
         <f aca="false">J332*J351</f>
@@ -55798,7 +55798,7 @@
       </c>
       <c r="E350" s="17" t="n">
         <f aca="false">E349/D349-1</f>
-        <v>0.787179227564467</v>
+        <v>0.787179227564469</v>
       </c>
       <c r="F350" s="17" t="n">
         <f aca="false">F349/E349-1</f>
@@ -55806,15 +55806,15 @@
       </c>
       <c r="G350" s="17" t="n">
         <f aca="false">G349/F349-1</f>
-        <v>0.233608153765065</v>
+        <v>0.233608153765066</v>
       </c>
       <c r="H350" s="25" t="n">
         <f aca="false">H349/G349-1</f>
-        <v>0.0031104192491378</v>
+        <v>0.00311041924913758</v>
       </c>
       <c r="I350" s="25" t="n">
         <f aca="false">I349/H349-1</f>
-        <v>-0.0478961937830137</v>
+        <v>-0.0478961937830134</v>
       </c>
       <c r="J350" s="25" t="n">
         <f aca="false">J349/I349-1</f>
@@ -55838,7 +55838,7 @@
       </c>
       <c r="E351" s="17" t="n">
         <f aca="false">E347/E332</f>
-        <v>0.144249396377643</v>
+        <v>0.144249396377644</v>
       </c>
       <c r="F351" s="17" t="n">
         <f aca="false">F347/F332</f>
@@ -55858,7 +55858,7 @@
       </c>
       <c r="J351" s="25" t="n">
         <f aca="false">$G351+(fade_mB-$G351)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55915,7 +55915,7 @@
       </c>
       <c r="D357" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E357" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56011,7 +56011,7 @@
       </c>
       <c r="D361" s="23" t="n">
         <f aca="false">D359*D360/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E361" s="23" t="n">
         <f aca="false">E359*E360/1000</f>
@@ -56130,7 +56130,7 @@
       </c>
       <c r="E366" s="22" t="n">
         <f aca="false">E362*E365</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F366" s="22" t="n">
         <f aca="false">F362*F365</f>
@@ -56234,7 +56234,7 @@
       </c>
       <c r="H370" s="24" t="n">
         <f aca="false">G370*(1+H371)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I370" s="24" t="n">
         <f aca="false">H370*(1+I371)</f>
@@ -56242,7 +56242,7 @@
       </c>
       <c r="J370" s="24" t="n">
         <f aca="false">I370*(1+J371)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K370" s="8" t="s">
         <v>446</v>
@@ -56277,7 +56277,7 @@
       </c>
       <c r="I371" s="25" t="n">
         <f aca="false">$G371+(fade_gB-$G371)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J371" s="25" t="n">
         <f aca="false">$G371+(fade_gB-$G371)*3/3</f>
@@ -56301,7 +56301,7 @@
       </c>
       <c r="E372" s="17" t="n">
         <f aca="false">E367/E370</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F372" s="17" t="n">
         <f aca="false">F367/F370</f>
@@ -56321,7 +56321,7 @@
       </c>
       <c r="D373" s="21" t="n">
         <f aca="false">D367/fx/D359*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E373" s="21" t="n">
         <f aca="false">E367/fx/E359*1000</f>
@@ -56333,7 +56333,7 @@
       </c>
       <c r="G373" s="21" t="n">
         <f aca="false">G367/fx/G359*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56400,11 +56400,11 @@
       </c>
       <c r="E377" s="22" t="n">
         <f aca="false">E367*E376+E369*$D$375</f>
-        <v>83.9769537919445</v>
+        <v>83.9769537919446</v>
       </c>
       <c r="F377" s="22" t="n">
         <f aca="false">F367*F376+F369*$D$375</f>
-        <v>91.7020397832931</v>
+        <v>91.7020397832932</v>
       </c>
       <c r="G377" s="22" t="n">
         <f aca="false">G367*G376+G369*$D$375</f>
@@ -56456,7 +56456,7 @@
       </c>
       <c r="E379" s="22" t="n">
         <f aca="false">D379*(1+MAX(0,phi*E371))</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F379" s="22" t="n">
         <f aca="false">E379*(1+MAX(0,phi*F371))</f>
@@ -56484,7 +56484,7 @@
       </c>
       <c r="E380" s="22" t="n">
         <f aca="false">E379+0*E370</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F380" s="22" t="n">
         <f aca="false">F379+0*F370</f>
@@ -56520,7 +56520,7 @@
       </c>
       <c r="G381" s="22" t="n">
         <f aca="false">G377-G380</f>
-        <v>68.6212975289841</v>
+        <v>68.6212975289842</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56624,7 +56624,7 @@
       </c>
       <c r="E385" s="22" t="n">
         <f aca="false">(E381+E383)*E384</f>
-        <v>41.3361586098714</v>
+        <v>41.3361586098715</v>
       </c>
       <c r="F385" s="22" t="n">
         <f aca="false">(F381+F383)*F384</f>
@@ -56632,7 +56632,7 @@
       </c>
       <c r="G385" s="22" t="n">
         <f aca="false">(G381+G383)*G384</f>
-        <v>54.8121861220279</v>
+        <v>54.812186122028</v>
       </c>
       <c r="H385" s="24" t="n">
         <f aca="false">H370*H389</f>
@@ -56640,7 +56640,7 @@
       </c>
       <c r="I385" s="24" t="n">
         <f aca="false">I370*I389</f>
-        <v>56.1048627069639</v>
+        <v>56.104862706964</v>
       </c>
       <c r="J385" s="24" t="n">
         <f aca="false">J370*J389</f>
@@ -56720,7 +56720,7 @@
       </c>
       <c r="I387" s="29" t="n">
         <f aca="false">I385/I386</f>
-        <v>24.7271454405864</v>
+        <v>24.7271454405865</v>
       </c>
       <c r="J387" s="29" t="n">
         <f aca="false">J385/J386</f>
@@ -56740,7 +56740,7 @@
       </c>
       <c r="E388" s="17" t="n">
         <f aca="false">E387/D387-1</f>
-        <v>0.664475686400785</v>
+        <v>0.664475686400787</v>
       </c>
       <c r="F388" s="17" t="n">
         <f aca="false">F387/E387-1</f>
@@ -56748,7 +56748,7 @@
       </c>
       <c r="G388" s="17" t="n">
         <f aca="false">G387/F387-1</f>
-        <v>0.201731803165717</v>
+        <v>0.201731803165718</v>
       </c>
       <c r="H388" s="25" t="n">
         <f aca="false">H387/G387-1</f>
@@ -56756,11 +56756,11 @@
       </c>
       <c r="I388" s="25" t="n">
         <f aca="false">I387/H387-1</f>
-        <v>-0.0108245162079031</v>
+        <v>-0.0108245162079028</v>
       </c>
       <c r="J388" s="25" t="n">
         <f aca="false">J387/I387-1</f>
-        <v>-0.0571816385202174</v>
+        <v>-0.0571816385202173</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56800,7 +56800,7 @@
       </c>
       <c r="J389" s="25" t="n">
         <f aca="false">$G389+(fade_mB-$G389)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56857,7 +56857,7 @@
       </c>
       <c r="D395" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E395" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -56953,7 +56953,7 @@
       </c>
       <c r="D399" s="23" t="n">
         <f aca="false">D397*D398/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E399" s="23" t="n">
         <f aca="false">E397*E398/1000</f>
@@ -57072,7 +57072,7 @@
       </c>
       <c r="E404" s="22" t="n">
         <f aca="false">E400*E403</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F404" s="22" t="n">
         <f aca="false">F400*F403</f>
@@ -57176,7 +57176,7 @@
       </c>
       <c r="H408" s="24" t="n">
         <f aca="false">G408*(1+H409)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I408" s="24" t="n">
         <f aca="false">H408*(1+I409)</f>
@@ -57184,7 +57184,7 @@
       </c>
       <c r="J408" s="24" t="n">
         <f aca="false">I408*(1+J409)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K408" s="8" t="s">
         <v>446</v>
@@ -57219,7 +57219,7 @@
       </c>
       <c r="I409" s="25" t="n">
         <f aca="false">$G409+(fade_gB-$G409)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J409" s="25" t="n">
         <f aca="false">$G409+(fade_gB-$G409)*3/3</f>
@@ -57243,7 +57243,7 @@
       </c>
       <c r="E410" s="17" t="n">
         <f aca="false">E405/E408</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F410" s="17" t="n">
         <f aca="false">F405/F408</f>
@@ -57263,7 +57263,7 @@
       </c>
       <c r="D411" s="21" t="n">
         <f aca="false">D405/fx/D397*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E411" s="21" t="n">
         <f aca="false">E405/fx/E397*1000</f>
@@ -57275,7 +57275,7 @@
       </c>
       <c r="G411" s="21" t="n">
         <f aca="false">G405/fx/G397*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57342,11 +57342,11 @@
       </c>
       <c r="E415" s="22" t="n">
         <f aca="false">E405*E414+E407*$D$413</f>
-        <v>87.1068948892879</v>
+        <v>87.106894889288</v>
       </c>
       <c r="F415" s="22" t="n">
         <f aca="false">F405*F414+F407*$D$413</f>
-        <v>97.0979292441669</v>
+        <v>97.097929244167</v>
       </c>
       <c r="G415" s="22" t="n">
         <f aca="false">G405*G414+G407*$D$413</f>
@@ -57398,7 +57398,7 @@
       </c>
       <c r="E417" s="22" t="n">
         <f aca="false">D417*(1+MAX(0,phi*E409))</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F417" s="22" t="n">
         <f aca="false">E417*(1+MAX(0,phi*F409))</f>
@@ -57426,7 +57426,7 @@
       </c>
       <c r="E418" s="22" t="n">
         <f aca="false">E417+0*E408</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F418" s="22" t="n">
         <f aca="false">F417+0*F408</f>
@@ -57454,15 +57454,15 @@
       </c>
       <c r="E419" s="22" t="n">
         <f aca="false">E415-E418</f>
-        <v>54.0196234787532</v>
+        <v>54.0196234787533</v>
       </c>
       <c r="F419" s="22" t="n">
         <f aca="false">F415-F418</f>
-        <v>61.9103596937454</v>
+        <v>61.9103596937455</v>
       </c>
       <c r="G419" s="22" t="n">
         <f aca="false">G415-G418</f>
-        <v>77.8414542926233</v>
+        <v>77.8414542926234</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57490,7 +57490,7 @@
       </c>
       <c r="G420" s="17" t="n">
         <f aca="false">G419/G408</f>
-        <v>0.199134167242807</v>
+        <v>0.199134167242808</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57566,23 +57566,23 @@
       </c>
       <c r="E423" s="22" t="n">
         <f aca="false">(E419+E421)*E422</f>
-        <v>43.7149138438524</v>
+        <v>43.7149138438525</v>
       </c>
       <c r="F423" s="22" t="n">
         <f aca="false">(F419+F421)*F422</f>
-        <v>49.7118733672465</v>
+        <v>49.7118733672466</v>
       </c>
       <c r="G423" s="22" t="n">
         <f aca="false">(G419+G421)*G422</f>
-        <v>61.8195052623937</v>
+        <v>61.8195052623938</v>
       </c>
       <c r="H423" s="24" t="n">
         <f aca="false">H408*H427</f>
-        <v>61.9659706709942</v>
+        <v>61.9659706709943</v>
       </c>
       <c r="I423" s="24" t="n">
         <f aca="false">I408*I427</f>
-        <v>58.942544386433</v>
+        <v>58.9425443864331</v>
       </c>
       <c r="J423" s="24" t="n">
         <f aca="false">J408*J427</f>
@@ -57658,11 +57658,11 @@
       </c>
       <c r="H425" s="29" t="n">
         <f aca="false">H423/H424</f>
-        <v>27.3103167037712</v>
+        <v>27.3103167037713</v>
       </c>
       <c r="I425" s="29" t="n">
         <f aca="false">I423/I424</f>
-        <v>25.9777993806701</v>
+        <v>25.9777993806702</v>
       </c>
       <c r="J425" s="29" t="n">
         <f aca="false">J423/J424</f>
@@ -57682,7 +57682,7 @@
       </c>
       <c r="E426" s="17" t="n">
         <f aca="false">E425/D425-1</f>
-        <v>0.760260596852394</v>
+        <v>0.760260596852396</v>
       </c>
       <c r="F426" s="17" t="n">
         <f aca="false">F425/E425-1</f>
@@ -57694,7 +57694,7 @@
       </c>
       <c r="H426" s="25" t="n">
         <f aca="false">H425/G425-1</f>
-        <v>0.00236924265211869</v>
+        <v>0.00236924265211891</v>
       </c>
       <c r="I426" s="25" t="n">
         <f aca="false">I425/H425-1</f>
@@ -57730,7 +57730,7 @@
       </c>
       <c r="G427" s="17" t="n">
         <f aca="false">G423/G408</f>
-        <v>0.158146784533491</v>
+        <v>0.158146784533492</v>
       </c>
       <c r="H427" s="25" t="n">
         <f aca="false">$G427+(fade_mB-$G427)*1/3</f>
@@ -57742,7 +57742,7 @@
       </c>
       <c r="J427" s="25" t="n">
         <f aca="false">$G427+(fade_mB-$G427)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57799,7 +57799,7 @@
       </c>
       <c r="D433" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E433" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -57895,7 +57895,7 @@
       </c>
       <c r="D437" s="23" t="n">
         <f aca="false">D435*D436/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E437" s="23" t="n">
         <f aca="false">E435*E436/1000</f>
@@ -58014,7 +58014,7 @@
       </c>
       <c r="E442" s="22" t="n">
         <f aca="false">E438*E441</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F442" s="22" t="n">
         <f aca="false">F438*F441</f>
@@ -58118,7 +58118,7 @@
       </c>
       <c r="H446" s="24" t="n">
         <f aca="false">G446*(1+H447)</f>
-        <v>404.861348045008</v>
+        <v>404.861348045009</v>
       </c>
       <c r="I446" s="24" t="n">
         <f aca="false">H446*(1+I447)</f>
@@ -58145,7 +58145,7 @@
       </c>
       <c r="E447" s="17" t="n">
         <f aca="false">E446/D446-1</f>
-        <v>0.404955400995315</v>
+        <v>0.404955400995316</v>
       </c>
       <c r="F447" s="17" t="n">
         <f aca="false">F446/E446-1</f>
@@ -58161,7 +58161,7 @@
       </c>
       <c r="I447" s="25" t="n">
         <f aca="false">$G447+(fade_gB-$G447)*2/3</f>
-        <v>0.0754105179978246</v>
+        <v>0.0754105179978245</v>
       </c>
       <c r="J447" s="25" t="n">
         <f aca="false">$G447+(fade_gB-$G447)*3/3</f>
@@ -58189,7 +58189,7 @@
       </c>
       <c r="F448" s="17" t="n">
         <f aca="false">F443/F446</f>
-        <v>0.565655387641132</v>
+        <v>0.565655387641133</v>
       </c>
       <c r="G448" s="17" t="n">
         <f aca="false">G443/G446</f>
@@ -58205,7 +58205,7 @@
       </c>
       <c r="D449" s="21" t="n">
         <f aca="false">D443/fx/D435*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E449" s="21" t="n">
         <f aca="false">E443/fx/E435*1000</f>
@@ -58217,7 +58217,7 @@
       </c>
       <c r="G449" s="21" t="n">
         <f aca="false">G443/fx/G435*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58284,11 +58284,11 @@
       </c>
       <c r="E453" s="22" t="n">
         <f aca="false">E443*E452+E445*$D$451</f>
-        <v>83.6309429198538</v>
+        <v>83.6309429198539</v>
       </c>
       <c r="F453" s="22" t="n">
         <f aca="false">F443*F452+F445*$D$451</f>
-        <v>90.5780216722052</v>
+        <v>90.5780216722053</v>
       </c>
       <c r="G453" s="22" t="n">
         <f aca="false">G443*G452+G445*$D$451</f>
@@ -58344,7 +58344,7 @@
       </c>
       <c r="F455" s="22" t="n">
         <f aca="false">E455*(1+MAX(0,phi*F447))</f>
-        <v>33.8037000601126</v>
+        <v>33.8037000601127</v>
       </c>
       <c r="G455" s="22" t="n">
         <f aca="false">F455*(1+MAX(0,phi*G447))</f>
@@ -58372,7 +58372,7 @@
       </c>
       <c r="F456" s="22" t="n">
         <f aca="false">F455+0*F446</f>
-        <v>33.8037000601126</v>
+        <v>33.8037000601127</v>
       </c>
       <c r="G456" s="22" t="n">
         <f aca="false">G455+0*G446</f>
@@ -58396,15 +58396,15 @@
       </c>
       <c r="E457" s="22" t="n">
         <f aca="false">E453-E456</f>
-        <v>51.2742669729899</v>
+        <v>51.27426697299</v>
       </c>
       <c r="F457" s="22" t="n">
         <f aca="false">F453-F456</f>
-        <v>56.7743216120926</v>
+        <v>56.7743216120927</v>
       </c>
       <c r="G457" s="22" t="n">
         <f aca="false">G453-G456</f>
-        <v>69.4801844087703</v>
+        <v>69.4801844087704</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58432,7 +58432,7 @@
       </c>
       <c r="G458" s="17" t="n">
         <f aca="false">G457/G446</f>
-        <v>0.190633289146532</v>
+        <v>0.190633289146533</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58508,7 +58508,7 @@
       </c>
       <c r="E461" s="22" t="n">
         <f aca="false">(E457+E459)*E460</f>
-        <v>41.6284428994723</v>
+        <v>41.6284428994724</v>
       </c>
       <c r="F461" s="22" t="n">
         <f aca="false">(F457+F459)*F460</f>
@@ -58516,7 +58516,7 @@
       </c>
       <c r="G461" s="22" t="n">
         <f aca="false">(G457+G459)*G460</f>
-        <v>55.4649401506654</v>
+        <v>55.4649401506655</v>
       </c>
       <c r="H461" s="24" t="n">
         <f aca="false">H446*H465</f>
@@ -58524,11 +58524,11 @@
       </c>
       <c r="I461" s="24" t="n">
         <f aca="false">I446*I465</f>
-        <v>53.1734677597664</v>
+        <v>53.1734677597665</v>
       </c>
       <c r="J461" s="24" t="n">
         <f aca="false">J446*J465</f>
-        <v>48.496560657433</v>
+        <v>48.4965606574331</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58592,11 +58592,11 @@
       </c>
       <c r="F463" s="23" t="n">
         <f aca="false">F461/F462</f>
-        <v>20.1892135929587</v>
+        <v>20.1892135929588</v>
       </c>
       <c r="G463" s="23" t="n">
         <f aca="false">G461/G462</f>
-        <v>24.4451118100444</v>
+        <v>24.4451118100445</v>
       </c>
       <c r="H463" s="29" t="n">
         <f aca="false">H461/H462</f>
@@ -58624,7 +58624,7 @@
       </c>
       <c r="E464" s="17" t="n">
         <f aca="false">E463/D463-1</f>
-        <v>0.676245045478129</v>
+        <v>0.676245045478131</v>
       </c>
       <c r="F464" s="17" t="n">
         <f aca="false">F463/E463-1</f>
@@ -58636,15 +58636,15 @@
       </c>
       <c r="H464" s="25" t="n">
         <f aca="false">H463/G463-1</f>
-        <v>0.00114082041403774</v>
+        <v>0.00114082041403729</v>
       </c>
       <c r="I464" s="25" t="n">
         <f aca="false">I463/H463-1</f>
-        <v>-0.0424063315877845</v>
+        <v>-0.0424063315877847</v>
       </c>
       <c r="J464" s="25" t="n">
         <f aca="false">J463/I463-1</f>
-        <v>-0.087955653437224</v>
+        <v>-0.0879556534372245</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58684,7 +58684,7 @@
       </c>
       <c r="J465" s="25" t="n">
         <f aca="false">$G465+(fade_mB-$G465)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58741,7 +58741,7 @@
       </c>
       <c r="D471" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E471" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -58837,7 +58837,7 @@
       </c>
       <c r="D475" s="23" t="n">
         <f aca="false">D473*D474/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E475" s="23" t="n">
         <f aca="false">E473*E474/1000</f>
@@ -58956,7 +58956,7 @@
       </c>
       <c r="E480" s="22" t="n">
         <f aca="false">E476*E479</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F480" s="22" t="n">
         <f aca="false">F476*F479</f>
@@ -59060,7 +59060,7 @@
       </c>
       <c r="H484" s="24" t="n">
         <f aca="false">G484*(1+H485)</f>
-        <v>458.174746021226</v>
+        <v>458.174746021227</v>
       </c>
       <c r="I484" s="24" t="n">
         <f aca="false">H484*(1+I485)</f>
@@ -59087,7 +59087,7 @@
       </c>
       <c r="E485" s="17" t="n">
         <f aca="false">E484/D484-1</f>
-        <v>0.467055400995315</v>
+        <v>0.467055400995316</v>
       </c>
       <c r="F485" s="17" t="n">
         <f aca="false">F484/E484-1</f>
@@ -59103,7 +59103,7 @@
       </c>
       <c r="I485" s="25" t="n">
         <f aca="false">$G485+(fade_gB-$G485)*2/3</f>
-        <v>0.0851916866963911</v>
+        <v>0.085191686696391</v>
       </c>
       <c r="J485" s="25" t="n">
         <f aca="false">$G485+(fade_gB-$G485)*3/3</f>
@@ -59131,7 +59131,7 @@
       </c>
       <c r="F486" s="17" t="n">
         <f aca="false">F481/F484</f>
-        <v>0.521659074521617</v>
+        <v>0.521659074521618</v>
       </c>
       <c r="G486" s="17" t="n">
         <f aca="false">G481/G484</f>
@@ -59147,7 +59147,7 @@
       </c>
       <c r="D487" s="21" t="n">
         <f aca="false">D481/fx/D473*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E487" s="21" t="n">
         <f aca="false">E481/fx/E473*1000</f>
@@ -59159,7 +59159,7 @@
       </c>
       <c r="G487" s="21" t="n">
         <f aca="false">G481/fx/G473*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59226,15 +59226,15 @@
       </c>
       <c r="E491" s="22" t="n">
         <f aca="false">E481*E490+E483*$D$489</f>
-        <v>86.4974150509974</v>
+        <v>86.4974150509975</v>
       </c>
       <c r="F491" s="22" t="n">
         <f aca="false">F481*F490+F483*$D$489</f>
-        <v>96.3969600984267</v>
+        <v>96.3969600984268</v>
       </c>
       <c r="G491" s="22" t="n">
         <f aca="false">G481*G490+G483*$D$489</f>
-        <v>115.609240142234</v>
+        <v>115.609240142235</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59342,11 +59342,11 @@
       </c>
       <c r="F495" s="22" t="n">
         <f aca="false">F491-F494</f>
-        <v>60.4907214141783</v>
+        <v>60.4907214141784</v>
       </c>
       <c r="G495" s="22" t="n">
         <f aca="false">G491-G494</f>
-        <v>75.2900334477918</v>
+        <v>75.2900334477919</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59450,19 +59450,19 @@
       </c>
       <c r="E499" s="22" t="n">
         <f aca="false">(E495+E497)*E498</f>
-        <v>42.9740828905567</v>
+        <v>42.9740828905568</v>
       </c>
       <c r="F499" s="22" t="n">
         <f aca="false">(F495+F497)*F498</f>
-        <v>48.6329482747755</v>
+        <v>48.6329482747756</v>
       </c>
       <c r="G499" s="22" t="n">
         <f aca="false">(G495+G497)*G498</f>
-        <v>59.8804254203218</v>
+        <v>59.8804254203219</v>
       </c>
       <c r="H499" s="24" t="n">
         <f aca="false">H484*H503</f>
-        <v>61.4823470132736</v>
+        <v>61.4823470132737</v>
       </c>
       <c r="I499" s="24" t="n">
         <f aca="false">I484*I503</f>
@@ -59538,11 +59538,11 @@
       </c>
       <c r="G501" s="23" t="n">
         <f aca="false">G499/G500</f>
-        <v>26.3911525128587</v>
+        <v>26.3911525128588</v>
       </c>
       <c r="H501" s="29" t="n">
         <f aca="false">H499/H500</f>
-        <v>27.0971688241404</v>
+        <v>27.0971688241405</v>
       </c>
       <c r="I501" s="29" t="n">
         <f aca="false">I499/I500</f>
@@ -59566,7 +59566,7 @@
       </c>
       <c r="E502" s="17" t="n">
         <f aca="false">E501/D501-1</f>
-        <v>0.73042968970082</v>
+        <v>0.730429689700822</v>
       </c>
       <c r="F502" s="17" t="n">
         <f aca="false">F501/E501-1</f>
@@ -59578,15 +59578,15 @@
       </c>
       <c r="H502" s="25" t="n">
         <f aca="false">H501/G501-1</f>
-        <v>0.0267520075501699</v>
+        <v>0.0267520075501697</v>
       </c>
       <c r="I502" s="25" t="n">
         <f aca="false">I501/H501-1</f>
-        <v>-0.024338069141851</v>
+        <v>-0.0243380691418511</v>
       </c>
       <c r="J502" s="25" t="n">
         <f aca="false">J501/I501-1</f>
-        <v>-0.0767524759027758</v>
+        <v>-0.0767524759027761</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59626,7 +59626,7 @@
       </c>
       <c r="J503" s="25" t="n">
         <f aca="false">$G503+(fade_mB-$G503)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59683,7 +59683,7 @@
       </c>
       <c r="D509" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E509" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -59779,7 +59779,7 @@
       </c>
       <c r="D513" s="23" t="n">
         <f aca="false">D511*D512/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E513" s="23" t="n">
         <f aca="false">E511*E512/1000</f>
@@ -59898,7 +59898,7 @@
       </c>
       <c r="E518" s="22" t="n">
         <f aca="false">E514*E517</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F518" s="22" t="n">
         <f aca="false">F514*F517</f>
@@ -60002,7 +60002,7 @@
       </c>
       <c r="H522" s="24" t="n">
         <f aca="false">G522*(1+H523)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I522" s="24" t="n">
         <f aca="false">H522*(1+I523)</f>
@@ -60010,7 +60010,7 @@
       </c>
       <c r="J522" s="24" t="n">
         <f aca="false">I522*(1+J523)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K522" s="8" t="s">
         <v>446</v>
@@ -60045,7 +60045,7 @@
       </c>
       <c r="I523" s="25" t="n">
         <f aca="false">$G523+(fade_gB-$G523)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J523" s="25" t="n">
         <f aca="false">$G523+(fade_gB-$G523)*3/3</f>
@@ -60069,7 +60069,7 @@
       </c>
       <c r="E524" s="17" t="n">
         <f aca="false">E519/E522</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F524" s="17" t="n">
         <f aca="false">F519/F522</f>
@@ -60089,7 +60089,7 @@
       </c>
       <c r="D525" s="21" t="n">
         <f aca="false">D519/fx/D511*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E525" s="21" t="n">
         <f aca="false">E519/fx/E511*1000</f>
@@ -60101,7 +60101,7 @@
       </c>
       <c r="G525" s="21" t="n">
         <f aca="false">G519/fx/G511*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60168,15 +60168,15 @@
       </c>
       <c r="E529" s="22" t="n">
         <f aca="false">E519*E528+E521*$D$527</f>
-        <v>85.5419243406162</v>
+        <v>85.5419243406163</v>
       </c>
       <c r="F529" s="22" t="n">
         <f aca="false">F519*F528+F521*$D$527</f>
-        <v>94.39998451373</v>
+        <v>94.3999845137301</v>
       </c>
       <c r="G529" s="22" t="n">
         <f aca="false">G519*G528+G521*$D$527</f>
-        <v>112.478765927812</v>
+        <v>112.478765927813</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60224,7 +60224,7 @@
       </c>
       <c r="E531" s="22" t="n">
         <f aca="false">D531*(1+MAX(0,phi*E523))</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F531" s="22" t="n">
         <f aca="false">E531*(1+MAX(0,phi*F523))</f>
@@ -60260,7 +60260,7 @@
       </c>
       <c r="G532" s="22" t="n">
         <f aca="false">G531+opx_adj_hi*G522</f>
-        <v>43.1563854129475</v>
+        <v>43.1563854129476</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60284,11 +60284,11 @@
       </c>
       <c r="F533" s="22" t="n">
         <f aca="false">F529-F532</f>
-        <v>55.8565461090086</v>
+        <v>55.8565461090087</v>
       </c>
       <c r="G533" s="22" t="n">
         <f aca="false">G529-G532</f>
-        <v>69.3223805148649</v>
+        <v>69.3223805148651</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60308,7 +60308,7 @@
       </c>
       <c r="E534" s="17" t="n">
         <f aca="false">E533/E522</f>
-        <v>0.160481498867934</v>
+        <v>0.160481498867935</v>
       </c>
       <c r="F534" s="17" t="n">
         <f aca="false">F533/F522</f>
@@ -60392,11 +60392,11 @@
       </c>
       <c r="E537" s="22" t="n">
         <f aca="false">(E533+E535)*E536</f>
-        <v>40.187127866331</v>
+        <v>40.1871278663311</v>
       </c>
       <c r="F537" s="22" t="n">
         <f aca="false">(F533+F535)*F536</f>
-        <v>45.1109750428465</v>
+        <v>45.1109750428466</v>
       </c>
       <c r="G537" s="22" t="n">
         <f aca="false">(G533+G535)*G536</f>
@@ -60404,11 +60404,11 @@
       </c>
       <c r="H537" s="24" t="n">
         <f aca="false">H522*H541</f>
-        <v>57.1177999689692</v>
+        <v>57.1177999689693</v>
       </c>
       <c r="I537" s="24" t="n">
         <f aca="false">I522*I541</f>
-        <v>56.3206345637578</v>
+        <v>56.3206345637579</v>
       </c>
       <c r="J537" s="24" t="n">
         <f aca="false">J522*J541</f>
@@ -60472,11 +60472,11 @@
       </c>
       <c r="E539" s="23" t="n">
         <f aca="false">E537/E538</f>
-        <v>17.7117081772462</v>
+        <v>17.7117081772463</v>
       </c>
       <c r="F539" s="23" t="n">
         <f aca="false">F537/F538</f>
-        <v>19.8817996699718</v>
+        <v>19.8817996699719</v>
       </c>
       <c r="G539" s="23" t="n">
         <f aca="false">G537/G538</f>
@@ -60508,7 +60508,7 @@
       </c>
       <c r="E540" s="17" t="n">
         <f aca="false">E539/D539-1</f>
-        <v>0.618207871493251</v>
+        <v>0.618207871493253</v>
       </c>
       <c r="F540" s="17" t="n">
         <f aca="false">F539/E539-1</f>
@@ -60516,19 +60516,19 @@
       </c>
       <c r="G540" s="17" t="n">
         <f aca="false">G539/F539-1</f>
-        <v>0.226863510237376</v>
+        <v>0.226863510237377</v>
       </c>
       <c r="H540" s="25" t="n">
         <f aca="false">H539/G539-1</f>
-        <v>0.0320316285709572</v>
+        <v>0.0320316285709568</v>
       </c>
       <c r="I540" s="25" t="n">
         <f aca="false">I539/H539-1</f>
-        <v>-0.0139565145303995</v>
+        <v>-0.0139565145303991</v>
       </c>
       <c r="J540" s="25" t="n">
         <f aca="false">J539/I539-1</f>
-        <v>-0.0607937013112644</v>
+        <v>-0.0607937013112643</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60568,7 +60568,7 @@
       </c>
       <c r="J541" s="25" t="n">
         <f aca="false">$G541+(fade_mB-$G541)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="544" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60625,7 +60625,7 @@
       </c>
       <c r="D547" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E547" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -60721,7 +60721,7 @@
       </c>
       <c r="D551" s="23" t="n">
         <f aca="false">D549*D550/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E551" s="23" t="n">
         <f aca="false">E549*E550/1000</f>
@@ -60840,7 +60840,7 @@
       </c>
       <c r="E556" s="22" t="n">
         <f aca="false">E552*E555</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F556" s="22" t="n">
         <f aca="false">F552*F555</f>
@@ -60944,7 +60944,7 @@
       </c>
       <c r="H560" s="24" t="n">
         <f aca="false">G560*(1+H561)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I560" s="24" t="n">
         <f aca="false">H560*(1+I561)</f>
@@ -60952,7 +60952,7 @@
       </c>
       <c r="J560" s="24" t="n">
         <f aca="false">I560*(1+J561)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K560" s="8" t="s">
         <v>446</v>
@@ -60987,7 +60987,7 @@
       </c>
       <c r="I561" s="25" t="n">
         <f aca="false">$G561+(fade_gB-$G561)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J561" s="25" t="n">
         <f aca="false">$G561+(fade_gB-$G561)*3/3</f>
@@ -61011,7 +61011,7 @@
       </c>
       <c r="E562" s="17" t="n">
         <f aca="false">E557/E560</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F562" s="17" t="n">
         <f aca="false">F557/F560</f>
@@ -61031,7 +61031,7 @@
       </c>
       <c r="D563" s="21" t="n">
         <f aca="false">D557/fx/D549*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E563" s="21" t="n">
         <f aca="false">E557/fx/E549*1000</f>
@@ -61043,7 +61043,7 @@
       </c>
       <c r="G563" s="21" t="n">
         <f aca="false">G557/fx/G549*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61110,15 +61110,15 @@
       </c>
       <c r="E567" s="22" t="n">
         <f aca="false">E557*E566+E559*$D$565</f>
-        <v>85.5419243406162</v>
+        <v>85.5419243406163</v>
       </c>
       <c r="F567" s="22" t="n">
         <f aca="false">F557*F566+F559*$D$565</f>
-        <v>94.39998451373</v>
+        <v>94.3999845137301</v>
       </c>
       <c r="G567" s="22" t="n">
         <f aca="false">G557*G566+G559*$D$565</f>
-        <v>112.478765927812</v>
+        <v>112.478765927813</v>
       </c>
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61174,7 +61174,7 @@
       </c>
       <c r="G569" s="22" t="n">
         <f aca="false">F569*(1+MAX(0,phi_hi*G561))</f>
-        <v>46.3246351962974</v>
+        <v>46.3246351962975</v>
       </c>
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61202,7 +61202,7 @@
       </c>
       <c r="G570" s="22" t="n">
         <f aca="false">G569+0*G560</f>
-        <v>46.3246351962974</v>
+        <v>46.3246351962975</v>
       </c>
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61222,11 +61222,11 @@
       </c>
       <c r="E571" s="22" t="n">
         <f aca="false">E567-E570</f>
-        <v>49.0788223798523</v>
+        <v>49.0788223798524</v>
       </c>
       <c r="F571" s="22" t="n">
         <f aca="false">F567-F570</f>
-        <v>54.6303289639752</v>
+        <v>54.6303289639753</v>
       </c>
       <c r="G571" s="22" t="n">
         <f aca="false">G567-G570</f>
@@ -61254,7 +61254,7 @@
       </c>
       <c r="F572" s="17" t="n">
         <f aca="false">F571/F560</f>
-        <v>0.162790416836391</v>
+        <v>0.162790416836392</v>
       </c>
       <c r="G572" s="17" t="n">
         <f aca="false">G571/G560</f>
@@ -61346,7 +61346,7 @@
       </c>
       <c r="H575" s="24" t="n">
         <f aca="false">H560*H579</f>
-        <v>55.3147617306531</v>
+        <v>55.3147617306532</v>
       </c>
       <c r="I575" s="24" t="n">
         <f aca="false">I560*I579</f>
@@ -61450,7 +61450,7 @@
       </c>
       <c r="E578" s="17" t="n">
         <f aca="false">E577/D577-1</f>
-        <v>0.609058329429819</v>
+        <v>0.609058329429821</v>
       </c>
       <c r="F578" s="17" t="n">
         <f aca="false">F577/E577-1</f>
@@ -61466,11 +61466,11 @@
       </c>
       <c r="I578" s="25" t="n">
         <f aca="false">I577/H577-1</f>
-        <v>0.000556499692767831</v>
+        <v>0.000556499692768053</v>
       </c>
       <c r="J578" s="25" t="n">
         <f aca="false">J577/I577-1</f>
-        <v>-0.0442465545805065</v>
+        <v>-0.0442465545805063</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61510,7 +61510,7 @@
       </c>
       <c r="J579" s="25" t="n">
         <f aca="false">$G579+(fade_mB-$G579)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61567,7 +61567,7 @@
       </c>
       <c r="D585" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E585" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -61663,7 +61663,7 @@
       </c>
       <c r="D589" s="23" t="n">
         <f aca="false">D587*D588/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E589" s="23" t="n">
         <f aca="false">E587*E588/1000</f>
@@ -61782,7 +61782,7 @@
       </c>
       <c r="E594" s="22" t="n">
         <f aca="false">E590*E593</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F594" s="22" t="n">
         <f aca="false">F590*F593</f>
@@ -61886,7 +61886,7 @@
       </c>
       <c r="H598" s="24" t="n">
         <f aca="false">G598*(1+H599)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I598" s="24" t="n">
         <f aca="false">H598*(1+I599)</f>
@@ -61894,7 +61894,7 @@
       </c>
       <c r="J598" s="24" t="n">
         <f aca="false">I598*(1+J599)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K598" s="8" t="s">
         <v>446</v>
@@ -61929,7 +61929,7 @@
       </c>
       <c r="I599" s="25" t="n">
         <f aca="false">$G599+(fade_gB-$G599)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J599" s="25" t="n">
         <f aca="false">$G599+(fade_gB-$G599)*3/3</f>
@@ -61953,7 +61953,7 @@
       </c>
       <c r="E600" s="17" t="n">
         <f aca="false">E595/E598</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F600" s="17" t="n">
         <f aca="false">F595/F598</f>
@@ -61973,7 +61973,7 @@
       </c>
       <c r="D601" s="21" t="n">
         <f aca="false">D595/fx/D587*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E601" s="21" t="n">
         <f aca="false">E595/fx/E587*1000</f>
@@ -61985,7 +61985,7 @@
       </c>
       <c r="G601" s="21" t="n">
         <f aca="false">G595/fx/G587*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62052,15 +62052,15 @@
       </c>
       <c r="E605" s="22" t="n">
         <f aca="false">E595*E604+E597*$D$603</f>
-        <v>85.5419243406162</v>
+        <v>85.5419243406163</v>
       </c>
       <c r="F605" s="22" t="n">
         <f aca="false">F595*F604+F597*$D$603</f>
-        <v>94.39998451373</v>
+        <v>94.3999845137301</v>
       </c>
       <c r="G605" s="22" t="n">
         <f aca="false">G595*G604+G597*$D$603</f>
-        <v>112.478765927812</v>
+        <v>112.478765927813</v>
       </c>
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62108,7 +62108,7 @@
       </c>
       <c r="E607" s="22" t="n">
         <f aca="false">D607*(1+MAX(0,phi*E599))</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F607" s="22" t="n">
         <f aca="false">E607*(1+MAX(0,phi*F599))</f>
@@ -62136,7 +62136,7 @@
       </c>
       <c r="E608" s="22" t="n">
         <f aca="false">E607+0*E598</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F608" s="22" t="n">
         <f aca="false">F607+0*F598</f>
@@ -62164,15 +62164,15 @@
       </c>
       <c r="E609" s="22" t="n">
         <f aca="false">E605-E608</f>
-        <v>52.4546529300815</v>
+        <v>52.4546529300816</v>
       </c>
       <c r="F609" s="22" t="n">
         <f aca="false">F605-F608</f>
-        <v>59.2124149633085</v>
+        <v>59.2124149633086</v>
       </c>
       <c r="G609" s="22" t="n">
         <f aca="false">G605-G608</f>
-        <v>73.2313759108037</v>
+        <v>73.2313759108038</v>
       </c>
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62192,7 +62192,7 @@
       </c>
       <c r="E610" s="17" t="n">
         <f aca="false">E609/E598</f>
-        <v>0.170481498867934</v>
+        <v>0.170481498867935</v>
       </c>
       <c r="F610" s="17" t="n">
         <f aca="false">F609/F598</f>
@@ -62280,19 +62280,19 @@
       </c>
       <c r="F613" s="22" t="n">
         <f aca="false">(F609+F611)*F612</f>
-        <v>45.7800629232152</v>
+        <v>45.7800629232153</v>
       </c>
       <c r="G613" s="22" t="n">
         <f aca="false">(G609+G611)*G612</f>
-        <v>56.0139044148867</v>
+        <v>56.0139044148868</v>
       </c>
       <c r="H613" s="24" t="n">
         <f aca="false">H598*H617</f>
-        <v>57.6186757421753</v>
+        <v>57.6186757421754</v>
       </c>
       <c r="I613" s="24" t="n">
         <f aca="false">I598*I617</f>
-        <v>56.5915101558983</v>
+        <v>56.5915101558984</v>
       </c>
       <c r="J613" s="24" t="n">
         <f aca="false">J598*J617</f>
@@ -62364,11 +62364,11 @@
       </c>
       <c r="G615" s="23" t="n">
         <f aca="false">G613/G614</f>
-        <v>24.6870573125935</v>
+        <v>24.6870573125936</v>
       </c>
       <c r="H615" s="29" t="n">
         <f aca="false">H613/H614</f>
-        <v>25.3943295897935</v>
+        <v>25.3943295897936</v>
       </c>
       <c r="I615" s="29" t="n">
         <f aca="false">I613/I614</f>
@@ -62392,7 +62392,7 @@
       </c>
       <c r="E616" s="17" t="n">
         <f aca="false">E615/D615-1</f>
-        <v>0.644774662351856</v>
+        <v>0.644774662351858</v>
       </c>
       <c r="F616" s="17" t="n">
         <f aca="false">F615/E615-1</f>
@@ -62400,11 +62400,11 @@
       </c>
       <c r="G616" s="17" t="n">
         <f aca="false">G615/F615-1</f>
-        <v>0.223543630965214</v>
+        <v>0.223543630965213</v>
       </c>
       <c r="H616" s="25" t="n">
         <f aca="false">H615/G615-1</f>
-        <v>0.0286495173663006</v>
+        <v>0.0286495173663008</v>
       </c>
       <c r="I616" s="25" t="n">
         <f aca="false">I615/H615-1</f>
@@ -62412,7 +62412,7 @@
       </c>
       <c r="J616" s="25" t="n">
         <f aca="false">J615/I615-1</f>
-        <v>-0.0652892177164378</v>
+        <v>-0.0652892177164376</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62452,7 +62452,7 @@
       </c>
       <c r="J617" s="25" t="n">
         <f aca="false">$G617+(fade_mB-$G617)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
     <row r="620" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62509,7 +62509,7 @@
       </c>
       <c r="D623" s="23" t="n">
         <f aca="false">itc_26*1</f>
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="E623" s="23" t="n">
         <f aca="false">itc_27*1*1</f>
@@ -62605,7 +62605,7 @@
       </c>
       <c r="D627" s="23" t="n">
         <f aca="false">D625*D626/1000</f>
-        <v>10.5297921189288</v>
+        <v>10.5297921189287</v>
       </c>
       <c r="E627" s="23" t="n">
         <f aca="false">E625*E626/1000</f>
@@ -62724,7 +62724,7 @@
       </c>
       <c r="E632" s="22" t="n">
         <f aca="false">E628*E631</f>
-        <v>140.847349380455</v>
+        <v>140.847349380456</v>
       </c>
       <c r="F632" s="22" t="n">
         <f aca="false">F628*F631</f>
@@ -62828,7 +62828,7 @@
       </c>
       <c r="H636" s="24" t="n">
         <f aca="false">G636*(1+H637)</f>
-        <v>439.064525134509</v>
+        <v>439.06452513451</v>
       </c>
       <c r="I636" s="24" t="n">
         <f aca="false">H636*(1+I637)</f>
@@ -62836,7 +62836,7 @@
       </c>
       <c r="J636" s="24" t="n">
         <f aca="false">I636*(1+J637)</f>
-        <v>493.891477207202</v>
+        <v>493.891477207203</v>
       </c>
       <c r="K636" s="8" t="s">
         <v>446</v>
@@ -62871,7 +62871,7 @@
       </c>
       <c r="I637" s="25" t="n">
         <f aca="false">$G637+(fade_gB-$G637)*2/3</f>
-        <v>0.081607882156467</v>
+        <v>0.0816078821564671</v>
       </c>
       <c r="J637" s="25" t="n">
         <f aca="false">$G637+(fade_gB-$G637)*3/3</f>
@@ -62895,7 +62895,7 @@
       </c>
       <c r="E638" s="17" t="n">
         <f aca="false">E633/E636</f>
-        <v>0.508626994782244</v>
+        <v>0.508626994782245</v>
       </c>
       <c r="F638" s="17" t="n">
         <f aca="false">F633/F636</f>
@@ -62915,7 +62915,7 @@
       </c>
       <c r="D639" s="21" t="n">
         <f aca="false">D633/fx/D625*1000</f>
-        <v>88.0716581635228</v>
+        <v>88.0716581635229</v>
       </c>
       <c r="E639" s="21" t="n">
         <f aca="false">E633/fx/E625*1000</f>
@@ -62927,7 +62927,7 @@
       </c>
       <c r="G639" s="21" t="n">
         <f aca="false">G633/fx/G625*1000</f>
-        <v>140.914653061636</v>
+        <v>140.914653061637</v>
       </c>
     </row>
     <row r="640" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62994,15 +62994,15 @@
       </c>
       <c r="E643" s="22" t="n">
         <f aca="false">E633*E642+E635*$D$641</f>
-        <v>85.5419243406162</v>
+        <v>85.5419243406163</v>
       </c>
       <c r="F643" s="22" t="n">
         <f aca="false">F633*F642+F635*$D$641</f>
-        <v>94.39998451373</v>
+        <v>94.3999845137301</v>
       </c>
       <c r="G643" s="22" t="n">
         <f aca="false">G633*G642+G635*$D$641</f>
-        <v>112.478765927812</v>
+        <v>112.478765927813</v>
       </c>
     </row>
     <row r="644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63050,7 +63050,7 @@
       </c>
       <c r="E645" s="22" t="n">
         <f aca="false">D645*(1+MAX(0,phi*E637))</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F645" s="22" t="n">
         <f aca="false">E645*(1+MAX(0,phi*F637))</f>
@@ -63078,7 +63078,7 @@
       </c>
       <c r="E646" s="22" t="n">
         <f aca="false">E645+0*E636</f>
-        <v>33.0872714105347</v>
+        <v>33.0872714105348</v>
       </c>
       <c r="F646" s="22" t="n">
         <f aca="false">F645+0*F636</f>
@@ -63106,15 +63106,15 @@
       </c>
       <c r="E647" s="22" t="n">
         <f aca="false">E643-E646</f>
-        <v>52.4546529300815</v>
+        <v>52.4546529300816</v>
       </c>
       <c r="F647" s="22" t="n">
         <f aca="false">F643-F646</f>
-        <v>59.2124149633085</v>
+        <v>59.2124149633086</v>
       </c>
       <c r="G647" s="22" t="n">
         <f aca="false">G643-G646</f>
-        <v>73.2313759108037</v>
+        <v>73.2313759108038</v>
       </c>
     </row>
     <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63134,7 +63134,7 @@
       </c>
       <c r="E648" s="17" t="n">
         <f aca="false">E647/E636</f>
-        <v>0.170481498867934</v>
+        <v>0.170481498867935</v>
       </c>
       <c r="F648" s="17" t="n">
         <f aca="false">F647/F636</f>
@@ -63226,15 +63226,15 @@
       </c>
       <c r="G651" s="22" t="n">
         <f aca="false">(G647+G649)*G650</f>
-        <v>59.8504732104269</v>
+        <v>59.850473210427</v>
       </c>
       <c r="H651" s="24" t="n">
         <f aca="false">H636*H655</f>
-        <v>60.4915387768565</v>
+        <v>60.4915387768566</v>
       </c>
       <c r="I651" s="24" t="n">
         <f aca="false">I636*I655</f>
-        <v>58.1451658072319</v>
+        <v>58.145165807232</v>
       </c>
       <c r="J651" s="24" t="n">
         <f aca="false">J636*J655</f>
@@ -63306,7 +63306,7 @@
       </c>
       <c r="G653" s="23" t="n">
         <f aca="false">G651/G652</f>
-        <v>26.3779516490725</v>
+        <v>26.3779516490726</v>
       </c>
       <c r="H653" s="29" t="n">
         <f aca="false">H651/H652</f>
@@ -63314,7 +63314,7 @@
       </c>
       <c r="I653" s="29" t="n">
         <f aca="false">I651/I652</f>
-        <v>25.6263700187965</v>
+        <v>25.6263700187966</v>
       </c>
       <c r="J653" s="29" t="n">
         <f aca="false">J651/J652</f>
@@ -63334,7 +63334,7 @@
       </c>
       <c r="E654" s="17" t="n">
         <f aca="false">E653/D653-1</f>
-        <v>0.757430461143079</v>
+        <v>0.757430461143081</v>
       </c>
       <c r="F654" s="17" t="n">
         <f aca="false">F653/E653-1</f>
@@ -63346,15 +63346,15 @@
       </c>
       <c r="H654" s="25" t="n">
         <f aca="false">H653/G653-1</f>
-        <v>0.010711119428843</v>
+        <v>0.0107111194288427</v>
       </c>
       <c r="I654" s="25" t="n">
         <f aca="false">I653/H653-1</f>
-        <v>-0.0387884490470649</v>
+        <v>-0.0387884490470645</v>
       </c>
       <c r="J654" s="25" t="n">
         <f aca="false">J653/I653-1</f>
-        <v>-0.0902649602239373</v>
+        <v>-0.0902649602239372</v>
       </c>
     </row>
     <row r="655" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63394,7 +63394,7 @@
       </c>
       <c r="J655" s="25" t="n">
         <f aca="false">$G655+(fade_mB-$G655)*3/3</f>
-        <v>0.107101857735107</v>
+        <v>0.107101857735108</v>
       </c>
     </row>
   </sheetData>

--- a/liteon/dist/20261025_光寶模型_v0.1.1.xlsx
+++ b/liteon/dist/20261025_光寶模型_v0.1.1.xlsx
@@ -7377,26 +7377,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7415,18 +7396,66 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D22:F22</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">唯讀台達電模型成品（本專案 </t>
+      <t xml:space="preserve">SIF_pwr_pkw_26</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Siliconomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">快照 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">In </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（本專案 </t>
     </r>
     <r>
       <rPr>
@@ -7464,7 +7493,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">內容權威；含機架電源櫃、</t>
+      <t xml:space="preserve">內容唯一值；含機架電源櫃、</t>
     </r>
     <r>
       <rPr>
@@ -7521,7 +7550,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">電源櫃）</t>
+      <t xml:space="preserve">電源櫃；口徑與台達電模型相同）</t>
     </r>
   </si>
   <si>
@@ -7595,26 +7624,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7633,18 +7643,18 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D23:F23</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同上；低／高亦取自台達電模型（</t>
+      <t xml:space="preserve">SIF_pwr_pkw_27</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上；低／高亦取自本庫（</t>
     </r>
     <r>
       <rPr>
@@ -7737,26 +7747,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7775,7 +7766,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D24:F24</t>
+      <t xml:space="preserve">SIF_pwr_pkw_28</t>
     </r>
   </si>
   <si>
@@ -7830,26 +7821,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">delta/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台達電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.2.1.xlsx</t>
+      <t xml:space="preserve">siliconomics</t>
     </r>
     <r>
       <rPr>
@@ -7868,7 +7840,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D25:F25</t>
+      <t xml:space="preserve">SIF_pwr_pkw_29</t>
     </r>
   </si>
   <si>
@@ -38006,7 +37978,7 @@
       <c r="H21" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="8" t="s">
         <v>93</v>
       </c>
     </row>
